--- a/Products family (1).xlsx
+++ b/Products family (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beyondbelievers-my.sharepoint.com/personal/k_saguem_z_systems/Documents/Bureau/Rehab app ( planner) - Copie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4856FE14-52B5-4CC7-B393-96E586131D57}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04ECAF1-36A5-4BEA-8228-97D51AD09D6B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6204" yWindow="3804" windowWidth="17280" windowHeight="8880" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
   </bookViews>
   <sheets>
     <sheet name="Famille-Produit" sheetId="1" r:id="rId1"/>
@@ -4135,7 +4135,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}">
-  <dimension ref="A1:C460"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C4145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
@@ -4155,7 +4156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str">
         <f>[1]Products!A930</f>
         <v>CF35250</v>
@@ -4169,7 +4170,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
         <f>[1]Products!A940</f>
         <v>ART00968</v>
@@ -4183,7 +4184,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
         <f>[1]Products!A1125</f>
         <v>CF35266</v>
@@ -4197,7 +4198,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="str">
         <f>[1]Products!A1126</f>
         <v>CF35267</v>
@@ -4211,7 +4212,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="str">
         <f>[1]Products!A1173</f>
         <v>CF35298</v>
@@ -4225,7 +4226,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
         <f>[1]Products!A1229</f>
         <v>CF35516</v>
@@ -4239,7 +4240,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="str">
         <f>[1]Products!A1257</f>
         <v>CF35517</v>
@@ -4253,7 +4254,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="str">
         <f>[1]Products!A1355</f>
         <v>CF35518</v>
@@ -4267,7 +4268,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="str">
         <f>[1]Products!A1422</f>
         <v>ART00221</v>
@@ -4281,7 +4282,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
         <f>[1]Products!A1423</f>
         <v>ART00222</v>
@@ -4295,7 +4296,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <f>[1]Products!A1424</f>
         <v>ART00223</v>
@@ -4309,7 +4310,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <f>[1]Products!A1425</f>
         <v>ART00224</v>
@@ -4323,7 +4324,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <f>[1]Products!A1426</f>
         <v>ART00225</v>
@@ -4337,7 +4338,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <f>[1]Products!A1427</f>
         <v>ART00226</v>
@@ -4351,7 +4352,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f>[1]Products!A1428</f>
         <v>ART00227</v>
@@ -4365,7 +4366,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="str">
         <f>[1]Products!A1429</f>
         <v>ART00228</v>
@@ -4379,7 +4380,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <f>[1]Products!A1430</f>
         <v>ART00229</v>
@@ -4393,7 +4394,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="str">
         <f>[1]Products!A1431</f>
         <v>ART00230</v>
@@ -4407,7 +4408,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <f>[1]Products!A1432</f>
         <v>ART00232</v>
@@ -4421,7 +4422,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="str">
         <f>[1]Products!A1487</f>
         <v>ART00294</v>
@@ -4435,7 +4436,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="str">
         <f>[1]Products!A1488</f>
         <v>ART00295</v>
@@ -4449,7 +4450,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="str">
         <f>[1]Products!A1539</f>
         <v>ART00356</v>
@@ -4463,7 +4464,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="str">
         <f>[1]Products!A1540</f>
         <v>ART00357</v>
@@ -4477,7 +4478,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="str">
         <f>[1]Products!A1652</f>
         <v>ART00525</v>
@@ -4491,7 +4492,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <f>[1]Products!A1684</f>
         <v>ART00523</v>
@@ -4505,7 +4506,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <f>[1]Products!A1685</f>
         <v>ART00524</v>
@@ -4519,7 +4520,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <f>[1]Products!A1689</f>
         <v>ART00530</v>
@@ -4533,7 +4534,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <f>[1]Products!A1690</f>
         <v>ART00531</v>
@@ -4547,7 +4548,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <f>[1]Products!A1691</f>
         <v>ART00532</v>
@@ -4561,7 +4562,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <f>[1]Products!A1833</f>
         <v>ART00682</v>
@@ -4575,7 +4576,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="str">
         <f>[1]Products!A1898</f>
         <v>ART00744</v>
@@ -4589,7 +4590,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="str">
         <f>[1]Products!A1899</f>
         <v>ART00745</v>
@@ -4603,7 +4604,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="str">
         <f>[1]Products!A1956</f>
         <v>ART00810</v>
@@ -4617,7 +4618,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="str">
         <f>[1]Products!A1957</f>
         <v>ART00811</v>
@@ -4631,7 +4632,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="str">
         <f>[1]Products!A2077</f>
         <v>ART00953</v>
@@ -4645,7 +4646,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="str">
         <f>[1]Products!A2095</f>
         <v>ART00969</v>
@@ -4659,7 +4660,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="str">
         <f>[1]Products!A2105</f>
         <v>ART00979</v>
@@ -4673,7 +4674,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="str">
         <f>[1]Products!A2280</f>
         <v>ART01161</v>
@@ -4687,7 +4688,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="str">
         <f>[1]Products!A2562</f>
         <v>ART01454</v>
@@ -4701,7 +4702,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="str">
         <f>[1]Products!A2583</f>
         <v>ART01475</v>
@@ -4715,7 +4716,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="str">
         <f>[1]Products!A2584</f>
         <v>ART01476</v>
@@ -4729,7 +4730,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="str">
         <f>[1]Products!A3230</f>
         <v>CF35524</v>
@@ -4743,7 +4744,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="str">
         <f>[1]Products!A3232</f>
         <v>CF35525</v>
@@ -4757,7 +4758,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="str">
         <f>[1]Products!A3233</f>
         <v>CF35529</v>
@@ -4771,7 +4772,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="str">
         <f>[1]Products!A3234</f>
         <v>CF35531</v>
@@ -4785,7 +4786,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="str">
         <f>[1]Products!A3518</f>
         <v>ART03301</v>
@@ -4799,7 +4800,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="str">
         <f>[1]Products!A3522</f>
         <v>ART03300</v>
@@ -4813,7 +4814,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="str">
         <f>[1]Products!A3523</f>
         <v>ART03302</v>
@@ -4827,7 +4828,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="str">
         <f>[1]Products!A4071</f>
         <v>CF35172</v>
@@ -4841,7 +4842,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="str">
         <f>[1]Products!A4075</f>
         <v>CF35217</v>
@@ -4855,7 +4856,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="str">
         <f>[1]Products!A4076</f>
         <v>CF35218</v>
@@ -4869,7 +4870,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="str">
         <f>[1]Products!A4077</f>
         <v>CF35219</v>
@@ -4883,7 +4884,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="str">
         <f>[1]Products!A4094</f>
         <v>CF35221</v>
@@ -4897,7 +4898,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="str">
         <f>[1]Products!A4095</f>
         <v>CF35226</v>
@@ -4911,7 +4912,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="str">
         <f>[1]Products!A4096</f>
         <v>CF35227</v>
@@ -4925,7 +4926,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="str">
         <f>[1]Products!A4097</f>
         <v>CF35235</v>
@@ -4939,7 +4940,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="str">
         <f>[1]Products!A4098</f>
         <v>CF35237</v>
@@ -4953,7 +4954,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="str">
         <f>[1]Products!A4099</f>
         <v>CF35238</v>
@@ -4967,7 +4968,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="str">
         <f>[1]Products!A4100</f>
         <v>CF35240</v>
@@ -4981,7 +4982,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="str">
         <f>[1]Products!A4101</f>
         <v>CF35241</v>
@@ -4995,7 +4996,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="str">
         <f>[1]Products!A4102</f>
         <v>CF35249</v>
@@ -5009,7 +5010,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="str">
         <f>[1]Products!A4105</f>
         <v>CF35901</v>
@@ -5023,7 +5024,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="str">
         <f>[1]Products!A4106</f>
         <v>CF35902</v>
@@ -5037,7 +5038,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="str">
         <f>[1]Products!A4107</f>
         <v>CF35903</v>
@@ -5051,7 +5052,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="str">
         <f>[1]Products!A4108</f>
         <v>CF35904</v>
@@ -5065,7 +5066,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="str">
         <f>[1]Products!A4109</f>
         <v>CF35914</v>
@@ -5079,7 +5080,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="str">
         <f>[1]Products!A4110</f>
         <v>CF35916</v>
@@ -5093,7 +5094,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="str">
         <f>[1]Products!A4178</f>
         <v>CF35208</v>
@@ -5107,7 +5108,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="str">
         <f>[1]Products!A4179</f>
         <v>CF35210</v>
@@ -5121,7 +5122,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="str">
         <f>[1]Products!A4180</f>
         <v>CF35212</v>
@@ -5135,7 +5136,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="str">
         <f>[1]Products!A4181</f>
         <v>CF35213</v>
@@ -5149,7 +5150,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="str">
         <f>[1]Products!A4183</f>
         <v>CF35900</v>
@@ -5163,7 +5164,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="str">
         <f>[1]Products!A4184</f>
         <v>CF35246</v>
@@ -5177,7 +5178,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="str">
         <f>[1]Products!A4185</f>
         <v>CF35245</v>
@@ -5191,7 +5192,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="str">
         <f>[1]Products!A4186</f>
         <v>CF35171</v>
@@ -5205,7 +5206,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="str">
         <f>[1]Products!A4187</f>
         <v>CF35198</v>
@@ -5219,7 +5220,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="str">
         <f>[1]Products!A4188</f>
         <v>CF35199</v>
@@ -5233,7 +5234,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="str">
         <f>[1]Products!A4190</f>
         <v>CF35223</v>
@@ -5247,7 +5248,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="str">
         <f>[1]Products!A4191</f>
         <v>CF35224</v>
@@ -5261,7 +5262,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="str">
         <f>[1]Products!A4192</f>
         <v>CF35225</v>
@@ -5275,7 +5276,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="str">
         <f>[1]Products!A4193</f>
         <v>CF35239</v>
@@ -5289,7 +5290,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="str">
         <f>[1]Products!A4194</f>
         <v>CF35242</v>
@@ -5303,7 +5304,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="str">
         <f>[1]Products!A4195</f>
         <v>CF35265</v>
@@ -5317,7 +5318,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="str">
         <f>[1]Products!A4196</f>
         <v>CF35530</v>
@@ -5331,7 +5332,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="str">
         <f>[1]Products!A4197</f>
         <v>CF35120</v>
@@ -5345,7 +5346,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="str">
         <f>[1]Products!A4198</f>
         <v>CF35121</v>
@@ -5359,7 +5360,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="str">
         <f>[1]Products!A4199</f>
         <v>CF35122</v>
@@ -5373,7 +5374,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="str">
         <f>[1]Products!A4200</f>
         <v>CF35178</v>
@@ -5387,7 +5388,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="str">
         <f>[1]Products!A4201</f>
         <v>CF35197</v>
@@ -5401,7 +5402,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="str">
         <f>[1]Products!A4202</f>
         <v>CF35118</v>
@@ -5415,7 +5416,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="str">
         <f>[1]Products!A4203</f>
         <v>CF35127</v>
@@ -5429,7 +5430,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="str">
         <f>[1]Products!A3631</f>
         <v>ART03422</v>
@@ -5443,7 +5444,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="str">
         <f>[1]Products!A3670</f>
         <v>ART03417</v>
@@ -5457,7 +5458,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="str">
         <f>[1]Products!A4063</f>
         <v>CF34026</v>
@@ -5471,7 +5472,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="str">
         <f>[1]Products!A4068</f>
         <v>CF34069</v>
@@ -5485,7 +5486,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="str">
         <f>[1]Products!A4070</f>
         <v>CF34070</v>
@@ -5499,7 +5500,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="str">
         <f>[1]Products!A4087</f>
         <v>CF34027</v>
@@ -5513,7 +5514,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="str">
         <f>[1]Products!A4088</f>
         <v>CF34029</v>
@@ -5527,7 +5528,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="str">
         <f>[1]Products!A4089</f>
         <v>CF34030</v>
@@ -5541,7 +5542,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="str">
         <f>[1]Products!A4090</f>
         <v>CF34046</v>
@@ -5555,7 +5556,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="str">
         <f>[1]Products!A4091</f>
         <v>CF34062</v>
@@ -5569,7 +5570,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="str">
         <f>[1]Products!A4092</f>
         <v>CF34063</v>
@@ -5583,7 +5584,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="str">
         <f>[1]Products!A4093</f>
         <v>CF34068</v>
@@ -5597,7 +5598,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="str">
         <f>[1]Products!A1098</f>
         <v>ART03641</v>
@@ -5611,7 +5612,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="str">
         <f>[1]Products!A1099</f>
         <v>ART03642</v>
@@ -5625,7 +5626,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="str">
         <f>[1]Products!A1100</f>
         <v>ART03643</v>
@@ -5639,7 +5640,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="str">
         <f>[1]Products!A1110</f>
         <v>ART03644</v>
@@ -5653,7 +5654,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="str">
         <f>[1]Products!A1117</f>
         <v>ART03645</v>
@@ -5667,7 +5668,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="str">
         <f>[1]Products!A1118</f>
         <v>ART03646</v>
@@ -5681,7 +5682,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="str">
         <f>[1]Products!A1119</f>
         <v>ART03647</v>
@@ -5695,7 +5696,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="str">
         <f>[1]Products!A1120</f>
         <v>ART03649</v>
@@ -5709,7 +5710,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="str">
         <f>[1]Products!A1121</f>
         <v>ART03650</v>
@@ -5723,7 +5724,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="str">
         <f>[1]Products!A1122</f>
         <v>ART03651</v>
@@ -5737,7 +5738,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="str">
         <f>[1]Products!A1123</f>
         <v>ART03652</v>
@@ -5751,7 +5752,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="str">
         <f>[1]Products!A1124</f>
         <v>ART03653</v>
@@ -5765,7 +5766,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="str">
         <f>[1]Products!A1415</f>
         <v>ART03648</v>
@@ -5779,7 +5780,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="str">
         <f>[1]Products!A1416</f>
         <v>ART03663</v>
@@ -5793,7 +5794,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="str">
         <f>[1]Products!A1417</f>
         <v>ART03675</v>
@@ -5807,7 +5808,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="str">
         <f>[1]Products!A3390</f>
         <v>ART03668</v>
@@ -5821,7 +5822,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="str">
         <f>[1]Products!A3422</f>
         <v>ART03996</v>
@@ -5835,7 +5836,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="str">
         <f>[1]Products!A3469</f>
         <v>ART03670</v>
@@ -5849,7 +5850,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="str">
         <f>[1]Products!A3759</f>
         <v>ART03658</v>
@@ -5863,7 +5864,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="str">
         <f>[1]Products!A3847</f>
         <v>ART03661</v>
@@ -5877,7 +5878,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="str">
         <f>[1]Products!A3848</f>
         <v>ART03673</v>
@@ -5891,7 +5892,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="str">
         <f>[1]Products!A3881</f>
         <v>ART03654</v>
@@ -5905,7 +5906,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="str">
         <f>[1]Products!A3882</f>
         <v>ART03655</v>
@@ -5919,7 +5920,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="str">
         <f>[1]Products!A3883</f>
         <v>ART03656</v>
@@ -5933,7 +5934,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="str">
         <f>[1]Products!A3884</f>
         <v>ART03657</v>
@@ -5947,7 +5948,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="str">
         <f>[1]Products!A3885</f>
         <v>ART03659</v>
@@ -5961,7 +5962,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="str">
         <f>[1]Products!A3886</f>
         <v>ART03660</v>
@@ -5975,7 +5976,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="str">
         <f>[1]Products!A3887</f>
         <v>ART03662</v>
@@ -5989,7 +5990,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="str">
         <f>[1]Products!A3888</f>
         <v>ART03664</v>
@@ -6003,7 +6004,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="str">
         <f>[1]Products!A3889</f>
         <v>ART03665</v>
@@ -6017,7 +6018,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="str">
         <f>[1]Products!A3890</f>
         <v>ART03666</v>
@@ -6031,7 +6032,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="str">
         <f>[1]Products!A3891</f>
         <v>ART03667</v>
@@ -6045,7 +6046,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="str">
         <f>[1]Products!A3892</f>
         <v>ART03669</v>
@@ -6059,7 +6060,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="str">
         <f>[1]Products!A3893</f>
         <v>ART03671</v>
@@ -6073,7 +6074,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="str">
         <f>[1]Products!A3894</f>
         <v>ART03672</v>
@@ -6087,7 +6088,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="str">
         <f>[1]Products!A3895</f>
         <v>ART03674</v>
@@ -6101,7 +6102,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="str">
         <f>[1]Products!A3896</f>
         <v>ART03676</v>
@@ -6115,7 +6116,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="str">
         <f>[1]Products!A3368</f>
         <v>ART03703</v>
@@ -6129,7 +6130,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="str">
         <f>[1]Products!A3462</f>
         <v>ART03704</v>
@@ -6143,7 +6144,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="str">
         <f>[1]Products!A3998</f>
         <v>ART03705</v>
@@ -6157,7 +6158,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="str">
         <f>[1]Products!A3999</f>
         <v>ART03706</v>
@@ -6171,7 +6172,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="str">
         <f>[1]Products!A4001</f>
         <v>ART03707</v>
@@ -6185,7 +6186,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="str">
         <f>[1]Products!A4009</f>
         <v>ART03984</v>
@@ -6199,7 +6200,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="str">
         <f>[1]Products!A94</f>
         <v>ART03709</v>
@@ -6213,7 +6214,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="str">
         <f>[1]Products!A100</f>
         <v>ART03711</v>
@@ -6227,7 +6228,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="str">
         <f>[1]Products!A1418</f>
         <v>ART03710</v>
@@ -6241,7 +6242,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="str">
         <f>[1]Products!A2310</f>
         <v>ART01192</v>
@@ -6255,7 +6256,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="str">
         <f>[1]Products!A2311</f>
         <v>ART01193</v>
@@ -6269,7 +6270,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="str">
         <f>[1]Products!A2312</f>
         <v>ART01194</v>
@@ -6283,7 +6284,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="str">
         <f>[1]Products!A2313</f>
         <v>ART01195</v>
@@ -6297,7 +6298,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="str">
         <f>[1]Products!A4052</f>
         <v>CF33352</v>
@@ -6311,7 +6312,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="str">
         <f>[1]Products!A4053</f>
         <v>CF33353</v>
@@ -6325,7 +6326,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="str">
         <f>[1]Products!A4054</f>
         <v>CF33354</v>
@@ -6339,7 +6340,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="str">
         <f>[1]Products!A4055</f>
         <v>CF33355</v>
@@ -6353,7 +6354,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="str">
         <f>[1]Products!A2499</f>
         <v>ART01389</v>
@@ -6367,7 +6368,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="str">
         <f>[1]Products!A2500</f>
         <v>ART01390</v>
@@ -6381,7 +6382,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="str">
         <f>[1]Products!A2501</f>
         <v>ART01391</v>
@@ -6395,7 +6396,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="str">
         <f>[1]Products!A2502</f>
         <v>ART01392</v>
@@ -6409,7 +6410,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="str">
         <f>[1]Products!A2758</f>
         <v>ART02965</v>
@@ -6423,7 +6424,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="str">
         <f>[1]Products!A2782</f>
         <v>ART02966</v>
@@ -6437,7 +6438,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="str">
         <f>[1]Products!A2783</f>
         <v>ART02967</v>
@@ -6451,7 +6452,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="str">
         <f>[1]Products!A2784</f>
         <v>ART02968</v>
@@ -6465,7 +6466,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="str">
         <f>[1]Products!A2785</f>
         <v>ART02969</v>
@@ -6479,7 +6480,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="str">
         <f>[1]Products!A2786</f>
         <v>ART02970</v>
@@ -6493,7 +6494,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="str">
         <f>[1]Products!A2787</f>
         <v>ART02971</v>
@@ -6507,7 +6508,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="str">
         <f>[1]Products!A3371</f>
         <v>ART03210</v>
@@ -6521,7 +6522,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="str">
         <f>[1]Products!A3372</f>
         <v>ART03211</v>
@@ -6535,7 +6536,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="str">
         <f>[1]Products!A3373</f>
         <v>ART03212</v>
@@ -6549,7 +6550,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="str">
         <f>[1]Products!A3676</f>
         <v>ART03447</v>
@@ -6563,7 +6564,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="str">
         <f>[1]Products!A614</f>
         <v>ART00513</v>
@@ -6577,7 +6578,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="str">
         <f>[1]Products!A1673</f>
         <v>ART00509</v>
@@ -6591,7 +6592,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="str">
         <f>[1]Products!A1675</f>
         <v>ART00512</v>
@@ -6605,7 +6606,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="str">
         <f>[1]Products!A3059</f>
         <v>ART02943</v>
@@ -6619,7 +6620,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="str">
         <f>[1]Products!A3060</f>
         <v>ART02944</v>
@@ -6633,7 +6634,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="str">
         <f>[1]Products!A3465</f>
         <v>ART03998</v>
@@ -6647,7 +6648,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="str">
         <f>[1]Products!A3475</f>
         <v>ART03999</v>
@@ -6661,7 +6662,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="str">
         <f>[1]Products!A1028</f>
         <v>ART03315</v>
@@ -6675,7 +6676,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="str">
         <f>[1]Products!A3803</f>
         <v>ART03498</v>
@@ -6689,7 +6690,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="str">
         <f>[1]Products!A3804</f>
         <v>ART03499</v>
@@ -6703,7 +6704,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="str">
         <f>[1]Products!A3805</f>
         <v>ART03500</v>
@@ -6717,7 +6718,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="str">
         <f>[1]Products!A289</f>
         <v>ART01381</v>
@@ -6731,7 +6732,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="str">
         <f>[1]Products!A648</f>
         <v>ART00014</v>
@@ -6745,7 +6746,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="str">
         <f>[1]Products!A685</f>
         <v>ART01873</v>
@@ -6759,7 +6760,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="str">
         <f>[1]Products!A793</f>
         <v>ART01902</v>
@@ -6773,7 +6774,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="str">
         <f>[1]Products!A2328</f>
         <v>ART01206</v>
@@ -6787,7 +6788,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="str">
         <f>[1]Products!A2329</f>
         <v>ART01210</v>
@@ -6801,7 +6802,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="str">
         <f>[1]Products!A2330</f>
         <v>ART01211</v>
@@ -6815,7 +6816,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="str">
         <f>[1]Products!A2573</f>
         <v>ART01453</v>
@@ -6829,7 +6830,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="str">
         <f>[1]Products!A2778</f>
         <v>ART02942</v>
@@ -6843,7 +6844,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="str">
         <f>[1]Products!A3180</f>
         <v>ART03164</v>
@@ -6857,7 +6858,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="str">
         <f>[1]Products!A3356</f>
         <v>ART03189</v>
@@ -7067,7 +7068,7 @@
         <v>Mio Matic</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="str">
         <f>[1]Products!A607</f>
         <v>ART00292</v>
@@ -7081,7 +7082,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="19.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="str">
         <f>[1]Products!A915</f>
         <v>ART01960</v>
@@ -7095,7 +7096,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="str">
         <f>[1]Products!A934</f>
         <v>ART01967</v>
@@ -7109,7 +7110,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="str">
         <f>[1]Products!A955</f>
         <v>ART01963</v>
@@ -7123,7 +7124,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="str">
         <f>[1]Products!A1088</f>
         <v>ART01968</v>
@@ -7137,7 +7138,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="str">
         <f>[1]Products!A1502</f>
         <v>ART00291</v>
@@ -7151,7 +7152,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="str">
         <f>[1]Products!A2977</f>
         <v>ART00299</v>
@@ -7165,7 +7166,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="str">
         <f>[1]Products!A2978</f>
         <v>ART00300</v>
@@ -7179,7 +7180,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="str">
         <f>[1]Products!A2988</f>
         <v>ART01985</v>
@@ -7193,7 +7194,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="str">
         <f>[1]Products!A3195</f>
         <v>ART01971</v>
@@ -7207,7 +7208,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="str">
         <f>[1]Products!A3444</f>
         <v>ART03997</v>
@@ -7221,7 +7222,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="str">
         <f>[1]Products!A946</f>
         <v>ART01972</v>
@@ -7235,7 +7236,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="str">
         <f>[1]Products!A1017</f>
         <v>ART02032</v>
@@ -7249,7 +7250,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="str">
         <f>[1]Products!A1067</f>
         <v>ART02059</v>
@@ -7263,7 +7264,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="str">
         <f>[1]Products!A2980</f>
         <v>ART01973</v>
@@ -7277,7 +7278,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="str">
         <f>[1]Products!A2981</f>
         <v>ART01974</v>
@@ -7291,7 +7292,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="str">
         <f>[1]Products!A2986</f>
         <v>ART01981</v>
@@ -7305,7 +7306,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="str">
         <f>[1]Products!A2987</f>
         <v>ART01982</v>
@@ -7319,7 +7320,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="str">
         <f>[1]Products!A2997</f>
         <v>ART02027</v>
@@ -7333,7 +7334,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="str">
         <f>[1]Products!A3000</f>
         <v>ART02701</v>
@@ -7347,7 +7348,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="str">
         <f>[1]Products!A3001</f>
         <v>ART02702</v>
@@ -7361,7 +7362,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="str">
         <f>[1]Products!A3002</f>
         <v>ART02703</v>
@@ -7375,7 +7376,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="str">
         <f>[1]Products!A3003</f>
         <v>ART02704</v>
@@ -7389,7 +7390,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="str">
         <f>[1]Products!A3004</f>
         <v>ART02705</v>
@@ -7403,7 +7404,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="str">
         <f>[1]Products!A3005</f>
         <v>ART02706</v>
@@ -7417,7 +7418,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="str">
         <f>[1]Products!A3006</f>
         <v>ART02707</v>
@@ -7431,7 +7432,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="str">
         <f>[1]Products!A3007</f>
         <v>ART02708</v>
@@ -7445,7 +7446,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="str">
         <f>[1]Products!A944</f>
         <v>ART02710</v>
@@ -7459,7 +7460,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="str">
         <f>[1]Products!A945</f>
         <v>ART02711</v>
@@ -7473,7 +7474,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="str">
         <f>[1]Products!A1012</f>
         <v>ART02712</v>
@@ -7487,7 +7488,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="str">
         <f>[1]Products!A2930</f>
         <v>ART02713</v>
@@ -7501,7 +7502,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="str">
         <f>[1]Products!A2931</f>
         <v>ART02714</v>
@@ -7515,7 +7516,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="str">
         <f>[1]Products!A2976</f>
         <v>ART00297</v>
@@ -7529,7 +7530,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="str">
         <f>[1]Products!A2992</f>
         <v>ART01989</v>
@@ -7543,7 +7544,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="str">
         <f>[1]Products!A2993</f>
         <v>ART01990</v>
@@ -7557,7 +7558,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="str">
         <f>[1]Products!A3008</f>
         <v>ART02709</v>
@@ -7571,7 +7572,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="str">
         <f>[1]Products!A3009</f>
         <v>ART02715</v>
@@ -7585,7 +7586,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="str">
         <f>[1]Products!A3010</f>
         <v>ART02716</v>
@@ -7599,7 +7600,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="str">
         <f>[1]Products!A3011</f>
         <v>ART02717</v>
@@ -7613,7 +7614,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="str">
         <f>[1]Products!A3025</f>
         <v>ART01991</v>
@@ -7627,7 +7628,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="str">
         <f>[1]Products!A201</f>
         <v>ART00103</v>
@@ -7641,7 +7642,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="str">
         <f>[1]Products!A283</f>
         <v>ART00301</v>
@@ -7655,7 +7656,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="str">
         <f>[1]Products!A362</f>
         <v>ART00134</v>
@@ -7669,7 +7670,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="str">
         <f>[1]Products!A421</f>
         <v>ART00333</v>
@@ -7683,7 +7684,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="str">
         <f>[1]Products!A479</f>
         <v>ART00186</v>
@@ -7697,7 +7698,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="str">
         <f>[1]Products!A1137</f>
         <v>ART00013</v>
@@ -7711,7 +7712,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="str">
         <f>[1]Products!A1199</f>
         <v>ART02125</v>
@@ -7725,7 +7726,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="str">
         <f>[1]Products!A1826</f>
         <v>ART00675</v>
@@ -7739,7 +7740,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="str">
         <f>[1]Products!A2001</f>
         <v>ART00857</v>
@@ -7753,7 +7754,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="str">
         <f>[1]Products!A2688</f>
         <v>ART02300</v>
@@ -7767,7 +7768,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="str">
         <f>[1]Products!A2689</f>
         <v>ART02140</v>
@@ -7781,7 +7782,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="str">
         <f>[1]Products!A2788</f>
         <v>ART02974</v>
@@ -7795,7 +7796,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="str">
         <f>[1]Products!A2835</f>
         <v>ART02973</v>
@@ -7809,7 +7810,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="str">
         <f>[1]Products!A3021</f>
         <v>ART03989</v>
@@ -7823,7 +7824,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="str">
         <f>[1]Products!A3045</f>
         <v>ART03988</v>
@@ -7837,7 +7838,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="str">
         <f>[1]Products!A3176</f>
         <v>ART02972</v>
@@ -7851,7 +7852,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="str">
         <f>[1]Products!A3397</f>
         <v>ART03213</v>
@@ -7865,7 +7866,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="str">
         <f>[1]Products!A3398</f>
         <v>ART03214</v>
@@ -7879,7 +7880,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="str">
         <f>[1]Products!A4046</f>
         <v>ART03986</v>
@@ -7893,7 +7894,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="str">
         <f>[1]Products!A4074</f>
         <v>ART03987</v>
@@ -7907,7 +7908,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="str">
         <f>[1]Products!A4170</f>
         <v>ART04049</v>
@@ -7921,7 +7922,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="str">
         <f>[1]Products!A4171</f>
         <v>ART04050</v>
@@ -7935,7 +7936,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="str">
         <f>[1]Products!A4172</f>
         <v>ART04051</v>
@@ -7949,7 +7950,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="str">
         <f>[1]Products!A4173</f>
         <v>ART04053</v>
@@ -7963,7 +7964,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="str">
         <f>[1]Products!A4174</f>
         <v>ART04052</v>
@@ -7977,7 +7978,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="str">
         <f>[1]Products!A4175</f>
         <v>ART04054</v>
@@ -7991,7 +7992,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="str">
         <f>[1]Products!A4176</f>
         <v>ART04055</v>
@@ -8005,7 +8006,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="str">
         <f>[1]Products!A4177</f>
         <v>ART04056</v>
@@ -8019,7 +8020,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="str">
         <f>[1]Products!A4189</f>
         <v>ART04048</v>
@@ -8033,7 +8034,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="str">
         <f>[1]Products!A3961</f>
         <v>ART03779</v>
@@ -8047,7 +8048,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="str">
         <f>[1]Products!A3975</f>
         <v>ART03780</v>
@@ -8061,7 +8062,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="str">
         <f>[1]Products!A3976</f>
         <v>ART03781</v>
@@ -8075,7 +8076,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="str">
         <f>[1]Products!A3977</f>
         <v>ART03782</v>
@@ -8089,7 +8090,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="str">
         <f>[1]Products!A3978</f>
         <v>ART03783</v>
@@ -8103,7 +8104,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="str">
         <f>[1]Products!A3979</f>
         <v>ART03784</v>
@@ -8117,7 +8118,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="str">
         <f>[1]Products!A3980</f>
         <v>ART03785</v>
@@ -8131,7 +8132,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="str">
         <f>[1]Products!A611</f>
         <v>ART03604</v>
@@ -8145,7 +8146,7 @@
         <v>Douceur</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="str">
         <f>[1]Products!A2776</f>
         <v>ART03603</v>
@@ -8159,7 +8160,7 @@
         <v>Douceur</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="str">
         <f>[1]Products!A320</f>
         <v>ART01203</v>
@@ -8173,7 +8174,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="str">
         <f>[1]Products!A447</f>
         <v>ART00956</v>
@@ -8187,7 +8188,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="str">
         <f>[1]Products!A629</f>
         <v>ART00009</v>
@@ -8201,7 +8202,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="str">
         <f>[1]Products!A647</f>
         <v>ART00008</v>
@@ -8215,7 +8216,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="str">
         <f>[1]Products!A707</f>
         <v>ART00007</v>
@@ -8229,7 +8230,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="str">
         <f>[1]Products!A708</f>
         <v>ART00011</v>
@@ -8243,7 +8244,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="str">
         <f>[1]Products!A779</f>
         <v>ART01130</v>
@@ -8257,7 +8258,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="str">
         <f>[1]Products!A1102</f>
         <v>ART00010</v>
@@ -8271,7 +8272,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="str">
         <f>[1]Products!A1588</f>
         <v>ART00409</v>
@@ -8285,7 +8286,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="str">
         <f>[1]Products!A1589</f>
         <v>ART00410</v>
@@ -8299,7 +8300,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="str">
         <f>[1]Products!A2084</f>
         <v>ART00955</v>
@@ -8313,7 +8314,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="str">
         <f>[1]Products!A2265</f>
         <v>ART01131</v>
@@ -8327,7 +8328,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="str">
         <f>[1]Products!A2319</f>
         <v>ART01201</v>
@@ -8341,7 +8342,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="str">
         <f>[1]Products!A2320</f>
         <v>ART01202</v>
@@ -8355,7 +8356,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="str">
         <f>[1]Products!A2321</f>
         <v>ART01204</v>
@@ -8369,7 +8370,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="str">
         <f>[1]Products!A2322</f>
         <v>ART01205</v>
@@ -8383,7 +8384,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="str">
         <f>[1]Products!A2430</f>
         <v>ART01311</v>
@@ -8397,7 +8398,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="str">
         <f>[1]Products!A2508</f>
         <v>ART01398</v>
@@ -8411,7 +8412,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="str">
         <f>[1]Products!A2509</f>
         <v>ART01399</v>
@@ -8425,7 +8426,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="str">
         <f>[1]Products!A2510</f>
         <v>ART01401</v>
@@ -8439,7 +8440,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="str">
         <f>[1]Products!A2514</f>
         <v>ART01402</v>
@@ -8453,7 +8454,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="str">
         <f>[1]Products!A2557</f>
         <v>ART01448</v>
@@ -8467,7 +8468,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="str">
         <f>[1]Products!A2759</f>
         <v>ART02951</v>
@@ -8481,7 +8482,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="str">
         <f>[1]Products!A2760</f>
         <v>ART02953</v>
@@ -8495,7 +8496,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="str">
         <f>[1]Products!A2761</f>
         <v>ART02952</v>
@@ -8509,7 +8510,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="str">
         <f>[1]Products!A2762</f>
         <v>ART02950</v>
@@ -8523,7 +8524,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="str">
         <f>[1]Products!A2769</f>
         <v>ART02960</v>
@@ -8537,7 +8538,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="str">
         <f>[1]Products!A2770</f>
         <v>ART02949</v>
@@ -8551,7 +8552,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="str">
         <f>[1]Products!A2771</f>
         <v>ART02962</v>
@@ -8565,7 +8566,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="str">
         <f>[1]Products!A2773</f>
         <v>ART02963</v>
@@ -8579,7 +8580,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="str">
         <f>[1]Products!A2781</f>
         <v>ART02961</v>
@@ -8593,7 +8594,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="str">
         <f>[1]Products!A2812</f>
         <v>ART02983</v>
@@ -8607,7 +8608,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="str">
         <f>[1]Products!A2901</f>
         <v>ART02959</v>
@@ -8621,7 +8622,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="str">
         <f>[1]Products!A3114</f>
         <v>ART03193</v>
@@ -8635,7 +8636,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="str">
         <f>[1]Products!A3116</f>
         <v>ART03203</v>
@@ -8649,7 +8650,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="str">
         <f>[1]Products!A3117</f>
         <v>ART03204</v>
@@ -8663,7 +8664,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="str">
         <f>[1]Products!A3118</f>
         <v>ART03205</v>
@@ -8677,7 +8678,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="str">
         <f>[1]Products!A3119</f>
         <v>ART03180</v>
@@ -8691,7 +8692,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="str">
         <f>[1]Products!A3171</f>
         <v>ART03163</v>
@@ -8705,7 +8706,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="str">
         <f>[1]Products!A3357</f>
         <v>ART03192</v>
@@ -8719,7 +8720,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="str">
         <f>[1]Products!A3381</f>
         <v>ART03207</v>
@@ -8733,7 +8734,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="str">
         <f>[1]Products!A3382</f>
         <v>ART03208</v>
@@ -8747,7 +8748,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="str">
         <f>[1]Products!A3383</f>
         <v>ART03209</v>
@@ -8761,7 +8762,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="str">
         <f>[1]Products!A3410</f>
         <v>ART03239</v>
@@ -8775,7 +8776,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="str">
         <f>[1]Products!A295</f>
         <v>ART01673</v>
@@ -8789,7 +8790,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="str">
         <f>[1]Products!A298</f>
         <v>ART01674</v>
@@ -8803,7 +8804,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="str">
         <f>[1]Products!A299</f>
         <v>ART01671</v>
@@ -8817,7 +8818,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="str">
         <f>[1]Products!A321</f>
         <v>ART01672</v>
@@ -8831,7 +8832,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="str">
         <f>[1]Products!A322</f>
         <v>ART01675</v>
@@ -8845,7 +8846,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="str">
         <f>[1]Products!A2422</f>
         <v>ART01304</v>
@@ -8859,7 +8860,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="str">
         <f>[1]Products!A2423</f>
         <v>ART01305</v>
@@ -8873,7 +8874,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="str">
         <f>[1]Products!A2424</f>
         <v>ART01306</v>
@@ -8887,7 +8888,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="str">
         <f>[1]Products!A2426</f>
         <v>ART01307</v>
@@ -8901,7 +8902,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="str">
         <f>[1]Products!A2427</f>
         <v>ART01308</v>
@@ -8915,7 +8916,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="str">
         <f>[1]Products!A2764</f>
         <v>ART02946</v>
@@ -8929,7 +8930,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="str">
         <f>[1]Products!A2765</f>
         <v>ART02947</v>
@@ -8943,7 +8944,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="str">
         <f>[1]Products!A2766</f>
         <v>ART02948</v>
@@ -8957,7 +8958,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="str">
         <f>[1]Products!A2777</f>
         <v>ART02945</v>
@@ -8971,7 +8972,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="str">
         <f>[1]Products!A34</f>
         <v>ART00049</v>
@@ -8985,7 +8986,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="str">
         <f>[1]Products!A35</f>
         <v>ART00052</v>
@@ -8999,7 +9000,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="str">
         <f>[1]Products!A47</f>
         <v>ART00050</v>
@@ -9013,7 +9014,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="str">
         <f>[1]Products!A531</f>
         <v>ART00051</v>
@@ -9027,7 +9028,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="str">
         <f>[1]Products!A2437</f>
         <v>ART01318</v>
@@ -9041,7 +9042,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="str">
         <f>[1]Products!A2443</f>
         <v>ART01326</v>
@@ -9055,7 +9056,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="str">
         <f>[1]Products!A2444</f>
         <v>ART01327</v>
@@ -9069,7 +9070,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="str">
         <f>[1]Products!A2445</f>
         <v>ART01328</v>
@@ -9083,7 +9084,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="str">
         <f>[1]Products!A2491</f>
         <v>ART01375</v>
@@ -9097,7 +9098,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="str">
         <f>[1]Products!A2492</f>
         <v>ART01376</v>
@@ -9111,7 +9112,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="str">
         <f>[1]Products!A2493</f>
         <v>ART01377</v>
@@ -9125,7 +9126,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="str">
         <f>[1]Products!A2494</f>
         <v>ART01378</v>
@@ -9139,7 +9140,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="str">
         <f>[1]Products!A2495</f>
         <v>ART01379</v>
@@ -9153,7 +9154,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="str">
         <f>[1]Products!A2496</f>
         <v>ART01380</v>
@@ -9167,7 +9168,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="str">
         <f>[1]Products!A3115</f>
         <v>ART00053</v>
@@ -9181,7 +9182,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="str">
         <f>[1]Products!A3950</f>
         <v>ART03744</v>
@@ -9195,7 +9196,7 @@
         <v>Blandoux</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="str">
         <f>[1]Products!A202</f>
         <v>ART01618</v>
@@ -9209,7 +9210,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="str">
         <f>[1]Products!A203</f>
         <v>ART01616</v>
@@ -9223,7 +9224,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="str">
         <f>[1]Products!A237</f>
         <v>ART01617</v>
@@ -9237,7 +9238,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="str">
         <f>[1]Products!A240</f>
         <v>ART01615</v>
@@ -9251,7 +9252,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="str">
         <f>[1]Products!A290</f>
         <v>ART00367</v>
@@ -9265,7 +9266,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="str">
         <f>[1]Products!A301</f>
         <v>ART01678</v>
@@ -9279,7 +9280,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="str">
         <f>[1]Products!A415</f>
         <v>ART00516</v>
@@ -9293,7 +9294,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="str">
         <f>[1]Products!A1309</f>
         <v>ART00369</v>
@@ -9307,7 +9308,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="str">
         <f>[1]Products!A1362</f>
         <v>ART02277</v>
@@ -9321,7 +9322,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="str">
         <f>[1]Products!A1548</f>
         <v>ART00365</v>
@@ -9335,7 +9336,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="str">
         <f>[1]Products!A1549</f>
         <v>ART00366</v>
@@ -9349,7 +9350,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="str">
         <f>[1]Products!A1550</f>
         <v>ART00368</v>
@@ -9363,7 +9364,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="str">
         <f>[1]Products!A1551</f>
         <v>ART00370</v>
@@ -9377,7 +9378,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="str">
         <f>[1]Products!A1552</f>
         <v>ART00371</v>
@@ -9391,7 +9392,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="str">
         <f>[1]Products!A1553</f>
         <v>ART00372</v>
@@ -9405,7 +9406,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="str">
         <f>[1]Products!A1554</f>
         <v>ART00373</v>
@@ -9419,7 +9420,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="str">
         <f>[1]Products!A1555</f>
         <v>ART00374</v>
@@ -9433,7 +9434,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="str">
         <f>[1]Products!A1676</f>
         <v>ART00514</v>
@@ -9447,7 +9448,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="str">
         <f>[1]Products!A1677</f>
         <v>ART00515</v>
@@ -9461,7 +9462,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="str">
         <f>[1]Products!A1678</f>
         <v>ART00517</v>
@@ -9475,7 +9476,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="str">
         <f>[1]Products!A1692</f>
         <v>ART00533</v>
@@ -9489,7 +9490,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="str">
         <f>[1]Products!A1708</f>
         <v>ART00546</v>
@@ -9503,7 +9504,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="str">
         <f>[1]Products!A1709</f>
         <v>ART00547</v>
@@ -9517,7 +9518,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="str">
         <f>[1]Products!A1954</f>
         <v>ART00807</v>
@@ -9531,7 +9532,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="str">
         <f>[1]Products!A3098</f>
         <v>ART03148</v>
@@ -9545,7 +9546,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="str">
         <f>[1]Products!A3245</f>
         <v>CF33017</v>
@@ -9559,7 +9560,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="str">
         <f>[1]Products!A3248</f>
         <v>CF33018</v>
@@ -9573,7 +9574,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="str">
         <f>[1]Products!A3250</f>
         <v>CF33019</v>
@@ -9587,7 +9588,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="str">
         <f>[1]Products!A3251</f>
         <v>CF33020</v>
@@ -9601,7 +9602,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="str">
         <f>[1]Products!A3254</f>
         <v>CF33000</v>
@@ -9615,7 +9616,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="str">
         <f>[1]Products!A3255</f>
         <v>CF33002</v>
@@ -9629,7 +9630,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="str">
         <f>[1]Products!A3256</f>
         <v>CF33003</v>
@@ -9643,7 +9644,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="str">
         <f>[1]Products!A3257</f>
         <v>CF33005</v>
@@ -9657,7 +9658,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="str">
         <f>[1]Products!A3258</f>
         <v>CF33006</v>
@@ -9671,7 +9672,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="str">
         <f>[1]Products!A3259</f>
         <v>CF33009</v>
@@ -9685,7 +9686,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="str">
         <f>[1]Products!A3260</f>
         <v>CF33010</v>
@@ -9699,7 +9700,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="str">
         <f>[1]Products!A3261</f>
         <v>CF33011</v>
@@ -9713,7 +9714,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="str">
         <f>[1]Products!A3262</f>
         <v>CF33013</v>
@@ -9727,7 +9728,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="str">
         <f>[1]Products!A3263</f>
         <v>CF33014</v>
@@ -9741,7 +9742,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="str">
         <f>[1]Products!A3264</f>
         <v>CF33015</v>
@@ -9755,7 +9756,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="str">
         <f>[1]Products!A3265</f>
         <v>CF33016</v>
@@ -9769,7 +9770,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="str">
         <f>[1]Products!A3266</f>
         <v>CF33021</v>
@@ -9783,7 +9784,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="str">
         <f>[1]Products!A3271</f>
         <v>CF33022</v>
@@ -9797,7 +9798,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="str">
         <f>[1]Products!A3273</f>
         <v>CF33023</v>
@@ -9811,7 +9812,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="str">
         <f>[1]Products!A3274</f>
         <v>CF33024</v>
@@ -9825,7 +9826,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="str">
         <f>[1]Products!A3275</f>
         <v>CF33025</v>
@@ -9839,7 +9840,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="str">
         <f>[1]Products!A3276</f>
         <v>CF33026</v>
@@ -9853,7 +9854,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="str">
         <f>[1]Products!A3277</f>
         <v>CF33027</v>
@@ -9867,7 +9868,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="str">
         <f>[1]Products!A3278</f>
         <v>CF33028</v>
@@ -9881,7 +9882,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="str">
         <f>[1]Products!A3279</f>
         <v>CF33029</v>
@@ -9895,7 +9896,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="str">
         <f>[1]Products!A3384</f>
         <v>CF33030</v>
@@ -9909,7 +9910,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="str">
         <f>[1]Products!A3385</f>
         <v>CF33031</v>
@@ -9923,7 +9924,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="str">
         <f>[1]Products!A3386</f>
         <v>CF33032</v>
@@ -9937,7 +9938,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="str">
         <f>[1]Products!A3387</f>
         <v>CF33033</v>
@@ -9951,7 +9952,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="str">
         <f>[1]Products!A3395</f>
         <v>CF33034</v>
@@ -9965,7 +9966,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="str">
         <f>[1]Products!A3396</f>
         <v>CF33035</v>
@@ -9979,7 +9980,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="str">
         <f>[1]Products!A3447</f>
         <v>CF33063</v>
@@ -9993,7 +9994,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="str">
         <f>[1]Products!A3586</f>
         <v>CF33071</v>
@@ -10007,7 +10008,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="str">
         <f>[1]Products!A3616</f>
         <v>CF33104</v>
@@ -10021,7 +10022,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="str">
         <f>[1]Products!A3618</f>
         <v>CF33072</v>
@@ -10035,7 +10036,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="str">
         <f>[1]Products!A3621</f>
         <v>CF33075</v>
@@ -10049,7 +10050,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="str">
         <f>[1]Products!A3626</f>
         <v>CF33076</v>
@@ -10063,7 +10064,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="str">
         <f>[1]Products!A3629</f>
         <v>CF33079</v>
@@ -10077,7 +10078,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="str">
         <f>[1]Products!A3630</f>
         <v>CF33081</v>
@@ -10091,7 +10092,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="str">
         <f>[1]Products!A3635</f>
         <v>CF33082</v>
@@ -10105,7 +10106,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="str">
         <f>[1]Products!A3636</f>
         <v>CF33083</v>
@@ -10119,7 +10120,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="str">
         <f>[1]Products!A3637</f>
         <v>CF33084</v>
@@ -10133,7 +10134,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="str">
         <f>[1]Products!A3638</f>
         <v>CF33086</v>
@@ -10147,7 +10148,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="str">
         <f>[1]Products!A3639</f>
         <v>CF33092</v>
@@ -10161,7 +10162,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="str">
         <f>[1]Products!A3641</f>
         <v>CF33097</v>
@@ -10175,7 +10176,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="str">
         <f>[1]Products!A3642</f>
         <v>CF33098</v>
@@ -10189,7 +10190,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="str">
         <f>[1]Products!A3643</f>
         <v>CF33099</v>
@@ -10203,7 +10204,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="str">
         <f>[1]Products!A3644</f>
         <v>CF33102</v>
@@ -10217,7 +10218,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="str">
         <f>[1]Products!A3645</f>
         <v>CF33105</v>
@@ -10231,7 +10232,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="str">
         <f>[1]Products!A3646</f>
         <v>CF33115</v>
@@ -10245,7 +10246,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="str">
         <f>[1]Products!A3647</f>
         <v>CF33116</v>
@@ -10259,7 +10260,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="str">
         <f>[1]Products!A3701</f>
         <v>CF33117</v>
@@ -10273,7 +10274,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="str">
         <f>[1]Products!A3702</f>
         <v>CF33125</v>
@@ -10287,7 +10288,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="str">
         <f>[1]Products!A3704</f>
         <v>CF33137</v>
@@ -10301,7 +10302,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="str">
         <f>[1]Products!A4032</f>
         <v>CF33319</v>
@@ -10315,7 +10316,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="str">
         <f>[1]Products!A4111</f>
         <v>CF400978</v>
@@ -10329,7 +10330,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="str">
         <f>[1]Products!A4112</f>
         <v>CF400980</v>
@@ -10343,7 +10344,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="str">
         <f>[1]Products!A4113</f>
         <v>CF401649</v>
@@ -10357,7 +10358,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="str">
         <f>[1]Products!A4114</f>
         <v>CF401651</v>
@@ -10371,7 +10372,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="str">
         <f>[1]Products!A4117</f>
         <v>CF33080</v>
@@ -10385,7 +10386,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="str">
         <f>[1]Products!A4118</f>
         <v>CF33112</v>
@@ -10399,7 +10400,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="str">
         <f>[1]Products!A4130</f>
         <v>CF401650</v>
@@ -10413,7 +10414,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="str">
         <f>[1]Products!A4131</f>
         <v>CF401648</v>
@@ -10427,7 +10428,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="str">
         <f>[1]Products!A4132</f>
         <v>CF400981</v>
@@ -10441,7 +10442,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="str">
         <f>[1]Products!A4133</f>
         <v>CF400979</v>
@@ -10455,7 +10456,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="str">
         <f>[1]Products!A4182</f>
         <v>CF33067</v>
@@ -10469,7 +10470,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="str">
         <f>[1]Products!A4056</f>
         <v>CF34000</v>
@@ -10482,7 +10483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="str">
         <f>[1]Products!A4057</f>
         <v>CF34001</v>
@@ -10495,7 +10496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="str">
         <f>[1]Products!A4058</f>
         <v>CF34002</v>
@@ -10508,7 +10509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="str">
         <f>[1]Products!A4059</f>
         <v>CF34006</v>
@@ -10521,7 +10522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="str">
         <f>[1]Products!A4060</f>
         <v>CF34007</v>
@@ -10534,7 +10535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="str">
         <f>[1]Products!A4061</f>
         <v>CF34008</v>
@@ -10547,7 +10548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="str">
         <f>[1]Products!A4062</f>
         <v>CF34009</v>
@@ -10560,7 +10561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="2">
         <f>[1]Products!A4205</f>
         <v>0</v>
@@ -10574,8 +10575,3699 @@
         <v/>
       </c>
     </row>
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="465" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="466" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="467" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="468" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="469" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="470" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="471" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="472" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="473" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="474" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="475" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="476" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="477" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="478" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="479" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="480" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="481" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="482" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="483" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="484" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="485" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="486" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="487" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="488" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="489" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="490" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="491" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="492" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="493" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="494" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="495" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="496" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="497" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="498" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="499" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="500" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="501" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="502" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="503" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="504" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="505" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="506" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="507" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="508" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="509" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="510" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="511" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="512" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="513" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="514" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="515" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="516" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="517" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="518" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="519" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="520" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="521" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="522" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="523" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="524" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="525" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="526" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="527" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="528" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="529" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="530" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="531" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="532" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="533" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="534" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="535" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="536" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="537" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="538" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="539" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="540" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="541" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="542" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="543" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="544" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="545" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="546" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="547" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="548" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="549" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="550" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="551" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="552" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="553" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="554" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="555" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="556" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="557" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="558" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="559" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="560" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="561" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="562" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="563" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="564" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="565" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="566" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="567" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="568" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="569" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="570" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="571" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="572" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="573" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="574" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="575" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="576" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="577" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="578" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="579" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="580" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="581" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="582" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="583" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="584" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="585" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="586" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="587" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="588" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="589" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="590" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="591" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="592" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="593" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="594" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="595" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="596" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="597" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="598" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="599" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="600" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="601" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="602" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="603" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="604" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="605" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="606" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="607" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="608" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="609" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="610" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="611" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="612" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="613" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="614" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="615" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="616" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="617" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="618" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="619" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="620" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="621" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="622" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="623" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="624" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="625" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="626" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="627" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="628" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="629" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="630" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="631" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="632" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="633" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="634" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="635" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="636" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="637" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="638" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="639" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="640" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="641" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="642" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="643" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="644" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="645" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="646" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="647" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="648" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="649" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="650" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="651" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="652" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="653" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="654" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="655" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="656" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="657" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="658" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="659" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="660" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="661" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="662" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="663" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="664" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="665" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="666" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="667" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="668" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="669" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="670" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="671" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="672" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="673" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="674" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="675" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="676" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="677" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="678" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="679" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="680" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="681" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="682" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="683" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="684" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="685" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="686" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="687" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="688" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="689" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="690" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="691" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="692" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="693" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="694" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="695" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="696" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="697" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="698" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="699" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="700" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="701" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="702" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="703" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="704" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="705" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="706" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="707" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="708" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="709" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="710" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="711" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="712" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="713" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="714" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="715" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="716" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="717" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="718" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="719" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="720" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="721" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="722" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="723" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="724" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="725" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="726" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="727" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="728" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="729" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="730" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="731" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="732" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="733" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="734" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="735" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="736" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="737" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="738" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="739" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="740" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="741" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="742" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="743" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="744" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="745" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="746" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="747" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="748" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="749" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="750" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="751" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="752" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="753" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="754" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="755" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="756" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="757" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="758" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="759" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="760" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="761" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="762" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="763" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="764" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="765" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="766" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="767" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="768" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="769" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="770" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="771" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="772" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="773" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="774" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="775" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="776" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="777" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="778" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="779" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="780" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="781" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="782" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="783" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="784" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="785" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="786" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="787" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="788" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="789" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="790" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="791" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="792" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="793" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="794" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="795" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="796" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="797" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="798" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="799" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="800" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="801" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="802" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="803" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="804" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="805" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="806" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="807" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="808" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="809" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="810" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="811" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="812" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="813" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="814" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="815" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="816" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="817" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="818" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="819" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="820" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="821" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="822" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="823" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="824" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="825" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="826" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="827" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="828" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="829" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="830" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="831" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="832" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="833" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="834" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="835" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="836" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="837" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="838" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="839" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="840" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="841" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="842" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="843" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="844" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="845" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="846" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="847" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="848" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="849" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="850" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="851" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="852" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="853" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="854" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="855" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="856" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="857" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="858" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="859" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="860" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="861" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="862" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="863" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="864" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="865" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="866" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="867" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="868" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="869" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="870" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="871" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="872" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="873" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="874" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="875" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="876" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="877" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="878" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="879" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="880" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="881" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="882" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="883" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="884" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="885" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="886" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="887" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="888" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="889" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="890" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="891" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="892" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="893" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="894" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="895" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="896" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="897" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="898" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="899" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="900" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="901" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="902" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="903" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="904" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="905" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="906" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="907" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="908" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="909" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="910" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="911" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="912" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="913" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="914" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="915" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="916" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="917" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="918" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="919" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="920" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="921" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="922" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="923" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="924" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="925" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="926" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="927" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="928" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="929" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="930" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="931" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="932" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="933" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="934" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="935" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="936" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="937" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="938" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="939" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="940" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="941" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="942" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="943" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="944" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="945" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="946" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="947" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="948" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="949" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="950" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="951" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="952" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="953" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="954" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="955" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="956" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="957" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="958" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="959" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="960" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="961" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="962" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="963" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="964" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="965" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="966" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="967" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="968" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="969" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="970" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="971" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="972" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="973" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="974" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="975" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="976" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="977" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="978" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="979" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="980" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="981" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="982" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="983" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="984" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="985" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="986" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="987" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="988" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="989" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="990" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="991" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="992" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="993" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="994" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="995" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="996" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="997" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="998" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="999" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1004" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1005" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1006" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1007" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1008" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1009" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1010" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1011" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1012" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1013" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1014" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1015" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1016" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1017" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1018" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1019" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1020" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1021" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1022" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1023" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1024" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1025" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1026" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1027" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1028" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1029" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1030" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1031" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1032" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1033" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1034" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1035" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1036" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1037" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1038" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1039" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1040" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1041" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1042" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1043" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1044" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1045" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1046" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1047" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1048" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1049" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1050" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1051" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1052" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1053" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1054" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1055" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1056" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1057" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1058" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1059" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1060" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1061" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1062" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1063" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1064" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1065" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1066" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1067" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1068" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1069" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1070" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1071" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1072" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1073" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1074" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1075" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1076" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1077" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1078" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1079" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1080" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1081" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1082" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1083" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1084" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1085" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1086" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1087" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1088" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1089" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1090" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1091" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1092" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1093" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1094" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1095" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1096" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1097" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1098" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1099" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1100" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1101" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1102" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1103" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1104" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1105" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1106" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1107" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1108" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1109" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1110" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1111" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1112" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1123" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1124" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1125" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1126" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1127" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1128" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1129" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1130" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1131" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1132" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1133" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1134" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1135" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1136" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1137" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1138" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1139" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1140" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1141" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1142" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1143" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1144" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1145" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1146" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1147" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1148" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1149" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1150" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1151" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1152" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1153" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1154" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1155" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1156" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1157" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1158" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1159" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1160" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1161" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1162" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1163" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1164" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1165" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1166" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1167" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1168" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1169" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1170" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1171" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1172" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1173" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1174" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1175" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1176" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1177" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1178" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1179" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1180" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1181" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1182" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1183" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1184" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1185" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1186" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1187" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1188" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1189" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1190" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1191" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1192" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1193" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1194" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1195" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1196" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1197" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1198" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1199" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1200" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1201" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1202" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1203" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1204" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1205" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1206" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1207" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1208" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1209" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1210" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1211" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1212" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1213" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1214" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1215" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1216" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1217" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1218" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1219" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1220" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1221" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1222" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1223" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1224" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1225" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1226" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1227" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1228" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1229" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1230" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1231" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1232" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1233" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1234" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1235" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1236" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1237" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1238" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1239" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1240" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1241" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1242" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1243" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1244" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1245" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1246" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1247" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1248" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1249" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1250" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1251" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1252" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1253" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1254" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1255" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1256" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1257" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1258" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1259" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1260" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1261" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1262" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1263" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1264" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1265" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1266" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1267" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1268" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1269" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1270" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1271" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1272" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1273" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1274" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1275" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1276" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1277" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1278" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1279" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1280" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1281" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1282" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1283" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1284" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1285" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1286" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1287" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1288" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1289" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1290" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1291" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1292" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1293" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1294" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1295" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1296" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1297" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1298" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1299" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1300" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1301" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1302" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1303" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1304" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1305" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1306" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1307" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1308" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1309" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1310" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1311" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1312" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1313" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1314" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1315" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1316" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1317" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1318" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1319" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1320" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1321" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1322" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1323" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1324" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1325" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1326" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1327" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1328" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1329" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1330" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1331" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1332" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1333" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1334" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1335" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1336" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1337" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1338" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1339" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1340" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1341" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1342" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1343" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1344" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1345" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1346" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1347" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1348" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1349" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1350" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1351" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1352" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1353" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1354" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1355" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1356" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1357" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1358" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1359" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1360" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1361" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1362" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1363" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1364" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1365" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1366" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1367" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1368" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1369" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1370" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1371" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1372" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1373" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1374" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1375" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1376" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1377" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1378" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1379" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1380" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1381" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1382" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1383" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1384" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1385" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1386" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1387" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1388" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1389" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1390" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1391" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1392" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1393" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1394" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1395" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1396" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1397" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1398" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1399" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1400" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1401" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1402" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1403" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1404" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1405" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1406" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1407" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1408" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1409" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1410" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1411" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1412" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1413" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1414" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1415" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1416" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1417" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1418" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1419" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1420" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1421" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1422" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1423" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1424" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1425" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1426" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1427" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1428" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1429" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1430" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1431" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1432" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1433" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1434" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1435" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1436" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1437" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1438" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1439" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1440" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1441" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1442" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1443" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1444" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1445" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1446" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1447" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1448" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1449" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1450" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1451" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1452" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1453" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1454" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1455" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1456" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1457" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1458" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1459" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1460" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1461" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1462" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1463" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1464" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1465" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1466" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1467" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1468" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1469" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1470" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1471" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1472" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1473" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1474" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1475" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1476" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1477" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1478" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1479" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1480" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1481" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1482" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1483" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1484" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1485" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1486" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1487" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1488" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1489" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1490" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1491" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1492" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1493" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1494" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1495" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1496" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1497" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1498" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1499" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1500" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1501" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1502" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1503" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1504" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1505" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1506" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1507" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1508" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1509" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1510" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1511" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1512" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1513" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1514" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1515" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1516" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1517" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1518" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1519" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1520" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1521" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1522" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1523" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1524" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1525" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1526" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1527" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1528" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1529" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1530" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1531" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1532" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1533" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1534" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1535" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1536" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1537" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1538" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1539" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1540" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1541" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1542" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1543" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1544" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1545" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1546" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1547" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1548" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1549" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1550" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1551" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1552" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1553" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1554" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1555" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1556" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1557" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1558" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1559" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1560" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1561" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1562" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1563" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1564" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1565" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1566" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1567" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1568" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1569" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1570" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1571" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1572" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1573" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1574" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1575" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1576" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1577" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1578" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1579" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1580" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1581" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1582" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1583" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1584" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1585" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1586" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1587" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1588" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1589" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1590" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1591" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1592" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1593" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1594" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1595" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1596" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1597" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1598" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1599" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1600" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1601" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1602" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1603" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1604" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1605" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1606" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1607" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1608" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1609" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1610" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1611" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1612" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1613" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1614" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1615" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1616" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1617" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1618" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1619" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1620" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1621" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1622" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1623" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1624" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1625" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1626" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1627" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1628" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1629" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1630" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1631" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1632" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1633" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1634" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1635" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1636" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1637" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1638" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1639" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1640" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1641" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1642" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1643" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1644" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1645" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1646" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1647" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1648" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1649" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1650" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1651" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1652" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1653" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1654" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1655" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1656" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1657" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1658" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1659" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1660" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1661" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1662" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1663" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1664" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1665" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1666" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1667" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1668" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1669" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1670" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1671" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1672" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1673" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1674" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1675" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1676" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1677" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1678" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1679" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1680" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1681" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1682" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1683" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1684" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1685" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1686" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1687" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1688" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1689" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1690" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1691" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1692" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1693" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1694" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1695" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1696" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1697" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1698" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1699" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1700" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1701" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1702" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1703" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1704" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1705" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1706" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1707" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1708" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1709" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1710" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1711" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1712" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1713" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1714" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1715" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1716" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1717" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1718" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1719" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1720" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1721" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1722" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1723" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1724" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1725" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1726" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1727" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1728" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1729" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1730" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1731" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1732" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1733" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1734" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1735" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1736" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1737" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1738" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1739" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1740" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1741" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1742" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1743" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1744" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1745" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1746" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1747" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1748" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1749" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1750" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1751" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1752" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1753" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1754" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1755" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1756" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1757" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1758" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1759" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1760" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1761" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1762" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1763" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1764" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1765" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1766" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1767" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1768" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1769" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1770" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1771" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1772" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1773" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1774" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1775" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1776" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1777" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1778" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1779" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1780" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1781" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1782" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1783" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1784" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1785" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1786" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1787" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1788" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1789" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1790" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1791" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1792" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1793" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1794" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1795" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1796" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1797" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1798" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1799" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1800" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1801" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1802" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1803" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1804" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1805" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1806" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1807" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1808" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1809" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1810" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1811" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1812" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1813" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1814" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1815" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1816" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1817" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1818" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1819" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1820" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1821" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1822" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1823" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1824" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1825" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1826" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1827" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1828" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1829" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1830" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1831" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1832" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1833" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1834" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1835" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1836" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1837" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1838" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1839" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1840" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1841" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1842" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1843" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1844" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1845" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1846" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1847" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1848" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1849" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1850" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1851" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1852" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1853" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1854" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1855" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1856" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1857" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1858" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1859" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1860" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1861" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1862" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1863" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1864" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1865" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1866" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1867" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1868" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1869" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1870" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1871" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1872" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1873" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1874" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1875" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1876" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1877" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1878" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1879" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1880" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1881" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1882" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1883" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1884" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1885" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1886" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1887" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1888" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1889" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1890" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1891" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1892" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1893" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1894" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1895" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1896" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1897" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1898" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1899" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1900" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1901" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1902" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1903" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1904" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1905" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1906" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1907" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1908" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1909" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1910" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1911" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1912" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1913" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1914" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1915" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1916" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1917" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1918" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1919" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1920" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1921" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1922" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1923" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1924" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1925" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1926" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1927" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1928" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1929" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1930" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1931" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1932" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1933" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1934" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1935" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1936" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1937" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1938" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1939" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1940" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1941" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1942" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1943" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1944" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1945" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1946" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1947" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1948" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1949" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1950" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1951" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1952" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1953" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1954" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1955" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1956" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1957" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1958" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1959" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1960" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1961" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1962" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1963" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1964" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1965" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1966" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1967" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1968" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1969" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1970" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1971" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1972" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1973" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1974" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1975" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1976" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1977" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1978" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1979" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1980" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1981" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1982" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1983" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1984" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1985" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1986" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1987" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1988" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1989" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1990" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1991" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1992" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1993" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1994" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1995" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1996" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1997" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1998" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="1999" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2000" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2001" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2002" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2003" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2004" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2005" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2006" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2007" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2008" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2009" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2010" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2011" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2012" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2013" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2014" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2015" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2016" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2017" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2018" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2019" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2020" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2021" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2022" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2023" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2024" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2025" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2026" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2027" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2028" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2029" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2030" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2031" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2032" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2033" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2034" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2035" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2036" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2037" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2038" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2039" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2040" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2041" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2042" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2043" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2044" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2045" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2046" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2047" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2048" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2049" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2050" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2051" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2052" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2053" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2054" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2055" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2056" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2057" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2058" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2059" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2060" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2061" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2062" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2063" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2064" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2065" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2066" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2067" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2068" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2069" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2070" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2071" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2072" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2073" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2074" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2075" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2076" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2077" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2078" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2079" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2080" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2081" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2082" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2083" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2084" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2085" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2086" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2087" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2088" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2089" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2090" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2091" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2092" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2093" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2094" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2095" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2096" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2097" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2098" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2099" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2100" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2101" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2102" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2103" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2104" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2105" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2106" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2107" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2108" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2109" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2110" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2111" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2112" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2123" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2124" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2125" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2126" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2127" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2128" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2129" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2130" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2131" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2132" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2133" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2134" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2135" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2136" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2137" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2138" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2139" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2140" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2141" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2142" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2143" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2144" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2145" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2146" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2147" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2148" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2149" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2150" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2151" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2152" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2153" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2154" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2155" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2156" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2157" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2158" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2159" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2160" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2161" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2162" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2163" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2164" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2165" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2166" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2167" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2168" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2169" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2170" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2171" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2172" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2173" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2174" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2175" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2176" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2177" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2178" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2179" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2180" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2181" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2182" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2183" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2184" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2185" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2186" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2187" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2188" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2189" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2190" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2191" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2192" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2193" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2194" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2195" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2196" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2197" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2198" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2199" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2200" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2201" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2202" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2203" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2204" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2205" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2206" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2207" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2208" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2209" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2210" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2211" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2212" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2213" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2214" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2215" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2216" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2217" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2218" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2219" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2220" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2221" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2222" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2223" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2224" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2225" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2226" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2227" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2228" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2229" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2230" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2231" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2232" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2233" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2234" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2235" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2236" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2237" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2238" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2239" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2240" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2241" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2242" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2243" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2244" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2245" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2246" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2247" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2248" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2249" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2250" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2251" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2252" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2253" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2254" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2255" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2256" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2257" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2258" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2259" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2260" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2261" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2262" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2263" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2264" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2265" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2266" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2267" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2268" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2269" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2270" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2271" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2272" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2273" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2274" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2275" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2276" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2277" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2278" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2279" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2280" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2281" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2282" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2283" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2284" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2285" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2286" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2287" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2288" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2289" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2290" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2291" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2292" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2293" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2294" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2295" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2296" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2297" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2298" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2299" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2300" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2301" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2302" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2303" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2304" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2305" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2306" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2307" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2308" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2309" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2310" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2311" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2312" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2313" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2314" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2315" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2316" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2317" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2318" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2319" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2320" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2321" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2322" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2323" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2324" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2325" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2326" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2327" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2328" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2329" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2330" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2331" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2332" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2333" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2334" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2335" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2336" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2337" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2338" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2339" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2340" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2341" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2342" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2343" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2344" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2345" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2346" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2347" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2348" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2349" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2350" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2351" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2352" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2353" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2354" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2355" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2356" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2357" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2358" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2359" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2360" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2361" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2362" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2363" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2364" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2365" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2366" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2367" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2368" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2369" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2370" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2371" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2372" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2373" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2374" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2375" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2376" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2377" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2378" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2379" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2380" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2381" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2382" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2383" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2384" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2385" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2386" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2387" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2388" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2389" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2390" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2391" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2392" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2393" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2394" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2395" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2396" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2397" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2398" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2399" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2400" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2401" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2402" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2403" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2404" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2405" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2406" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2407" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2408" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2409" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2410" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2411" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2412" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2413" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2414" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2415" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2416" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2417" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2418" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2419" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2420" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2421" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2422" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2423" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2424" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2425" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2426" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2427" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2428" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2429" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2430" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2431" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2432" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2433" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2434" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2435" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2436" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2437" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2438" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2439" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2440" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2441" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2442" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2443" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2444" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2445" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2446" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2447" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2448" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2449" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2450" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2451" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2452" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2453" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2454" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2455" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2456" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2457" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2458" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2459" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2460" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2461" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2462" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2463" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2464" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2465" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2466" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2467" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2468" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2469" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2470" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2471" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2472" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2473" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2474" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2475" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2476" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2477" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2478" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2479" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2480" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2481" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2482" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2483" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2484" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2485" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2486" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2487" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2488" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2489" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2490" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2491" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2492" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2493" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2494" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2495" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2496" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2497" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2498" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2499" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2500" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2501" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2502" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2503" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2504" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2505" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2506" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2507" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2508" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2509" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2510" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2511" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2512" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2513" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2514" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2515" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2516" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2517" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2518" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2519" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2520" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2521" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2522" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2523" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2524" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2525" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2526" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2527" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2528" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2529" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2530" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2531" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2532" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2533" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2534" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2535" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2536" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2537" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2538" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2539" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2540" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2541" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2542" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2543" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2544" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2545" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2546" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2547" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2548" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2549" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2550" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2551" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2552" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2553" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2554" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2555" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2556" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2557" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2558" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2559" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2560" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2561" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2562" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2563" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2564" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2565" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2566" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2567" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2568" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2569" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2570" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2571" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2572" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2573" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2574" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2575" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2576" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2577" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2578" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2579" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2580" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2581" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2582" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2583" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2584" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2585" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2586" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2587" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2588" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2589" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2590" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2591" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2592" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2593" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2594" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2595" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2596" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2597" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2598" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2599" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2600" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2601" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2602" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2603" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2604" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2605" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2606" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2607" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2608" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2609" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2610" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2611" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2612" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2613" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2614" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2615" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2616" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2617" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2618" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2619" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2620" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2621" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2622" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2623" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2624" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2625" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2626" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2627" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2628" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2629" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2630" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2631" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2632" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2633" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2634" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2635" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2636" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2637" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2638" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2639" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2640" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2641" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2642" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2643" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2644" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2645" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2646" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2647" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2648" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2649" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2650" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2651" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2652" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2653" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2654" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2655" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2656" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2657" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2658" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2659" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2660" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2661" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2662" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2663" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2664" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2665" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2666" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2667" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2668" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2669" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2670" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2671" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2672" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2673" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2674" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2675" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2676" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2677" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2678" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2679" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2680" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2681" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2682" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2683" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2684" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2685" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2686" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2687" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2688" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2689" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2690" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2691" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2692" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2693" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2694" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2695" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2696" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2697" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2698" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2699" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2700" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2701" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2702" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2703" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2704" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2705" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2706" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2707" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2708" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2709" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2710" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2711" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2712" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2713" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2714" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2715" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2716" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2717" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2718" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2719" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2720" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2721" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2722" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2723" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2724" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2725" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2726" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2727" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2728" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2729" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2730" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2731" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2732" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2733" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2734" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2735" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2736" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2737" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2738" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2739" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2740" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2741" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2742" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2743" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2744" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2745" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2746" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2747" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2748" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2749" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2750" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2751" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2752" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2753" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2754" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2755" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2756" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2757" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2758" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2759" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2760" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2761" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2762" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2763" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2764" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2765" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2766" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2767" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2768" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2769" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2770" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2771" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2772" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2773" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2774" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2775" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2776" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2777" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2778" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2779" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2780" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2781" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2782" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2783" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2784" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2785" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2786" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2787" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2788" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2789" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2790" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2791" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2792" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2793" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2794" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2795" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2796" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2797" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2798" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2799" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2800" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2801" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2802" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2803" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2804" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2805" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2806" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2807" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2808" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2809" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2810" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2811" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2812" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2813" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2814" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2815" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2816" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2817" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2818" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2819" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2820" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2821" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2822" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2823" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2824" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2825" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2826" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2827" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2828" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2829" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2830" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2831" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2832" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2833" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2834" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2835" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2836" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2837" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2838" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2839" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2840" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2841" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2842" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2843" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2844" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2845" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2846" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2847" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2848" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2849" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2850" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2851" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2852" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2853" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2854" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2855" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2856" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2857" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2858" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2859" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2860" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2861" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2862" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2863" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2864" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2865" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2866" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2867" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2868" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2869" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2870" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2871" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2872" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2873" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2874" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2875" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2876" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2877" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2878" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2879" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2880" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2881" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2882" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2883" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2884" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2885" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2886" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2887" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2888" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2889" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2890" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2891" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2892" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2893" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2894" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2895" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2896" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2897" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2898" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2899" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2900" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2901" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2902" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2903" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2904" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2905" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2906" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2907" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2908" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2909" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2910" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2911" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2912" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2913" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2914" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2915" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2916" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2917" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2918" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2919" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2920" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2921" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2922" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2923" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2924" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2925" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2926" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2927" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2928" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2929" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2930" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2931" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2932" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2933" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2934" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2935" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2936" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2937" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2938" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2939" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2940" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2941" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2942" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2943" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2944" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2945" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2946" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2947" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2948" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2949" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2950" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2951" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2952" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2953" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2954" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2955" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2956" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2957" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2958" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2959" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2960" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2961" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2962" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2963" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2964" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2965" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2966" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2967" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2968" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2969" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2970" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2971" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2972" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2973" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2974" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2975" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2976" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2977" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2978" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2979" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2980" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2981" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2982" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2983" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2984" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2985" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2986" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2987" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2988" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2989" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2990" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2991" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2992" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2993" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2994" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2995" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2996" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2997" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2998" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="2999" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3000" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3001" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3002" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3003" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3004" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3005" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3006" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3007" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3008" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3009" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3010" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3011" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3012" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3013" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3014" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3015" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3016" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3017" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3018" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3019" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3020" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3021" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3022" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3023" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3024" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3025" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3026" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3027" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3028" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3029" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3030" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3031" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3032" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3033" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3034" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3035" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3036" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3037" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3038" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3039" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3040" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3041" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3042" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3043" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3044" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3045" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3046" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3047" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3048" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3049" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3050" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3051" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3052" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3053" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3054" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3055" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3056" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3057" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3058" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3059" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3060" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3061" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3062" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3063" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3064" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3065" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3066" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3067" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3068" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3069" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3070" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3071" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3072" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3073" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3074" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3075" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3076" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3077" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3078" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3079" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3080" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3081" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3082" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3083" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3084" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3085" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3086" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3087" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3088" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3089" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3090" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3091" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3092" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3093" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3094" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3095" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3096" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3097" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3098" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3099" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3100" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3101" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3102" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3103" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3104" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3105" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3106" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3107" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3108" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3109" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3110" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3111" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3112" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3123" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3124" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3125" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3126" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3127" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3128" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3129" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3130" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3131" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3132" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3133" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3134" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3135" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3136" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3137" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3138" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3139" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3140" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3141" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3142" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3143" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3144" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3145" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3146" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3147" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3148" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3149" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3150" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3151" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3152" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3153" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3154" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3155" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3156" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3157" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3158" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3159" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3160" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3161" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3162" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3163" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3164" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3165" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3166" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3167" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3168" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3169" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3170" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3171" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3172" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3173" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3174" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3175" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3176" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3177" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3178" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3179" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3180" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3181" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3182" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3183" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3184" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3185" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3186" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3187" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3188" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3189" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3190" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3191" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3192" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3193" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3194" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3195" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3196" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3197" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3198" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3199" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3200" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3201" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3202" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3203" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3204" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3205" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3206" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3207" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3208" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3209" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3210" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3211" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3212" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3213" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3214" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3215" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3216" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3217" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3218" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3219" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3220" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3221" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3222" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3223" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3224" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3225" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3226" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3227" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3228" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3229" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3230" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3231" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3232" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3233" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3234" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3235" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3236" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3237" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3238" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3239" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3240" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3241" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3242" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3243" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3244" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3245" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3246" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3247" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3248" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3249" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3250" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3251" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3252" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3253" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3254" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3255" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3256" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3257" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3258" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3259" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3260" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3261" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3262" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3263" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3264" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3265" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3266" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3267" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3268" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3269" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3270" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3271" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3272" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3273" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3274" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3275" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3276" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3277" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3278" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3279" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3280" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3281" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3282" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3283" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3284" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3285" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3286" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3287" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3288" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3289" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3290" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3291" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3292" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3293" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3294" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3295" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3296" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3297" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3298" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3299" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3300" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3301" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3302" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3303" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3304" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3305" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3306" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3307" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3308" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3309" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3310" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3311" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3312" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3313" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3314" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3315" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3316" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3317" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3318" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3319" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3320" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3321" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3322" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3323" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3324" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3325" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3326" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3327" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3328" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3329" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3330" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3331" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3332" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3333" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3334" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3335" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3336" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3337" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3338" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3339" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3340" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3341" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3342" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3343" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3344" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3345" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3346" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3347" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3348" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3349" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3350" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3351" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3352" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3353" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3354" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3355" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3356" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3357" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3358" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3359" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3360" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3361" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3362" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3363" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3364" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3365" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3366" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3367" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3368" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3369" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3370" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3371" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3372" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3373" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3374" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3375" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3376" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3377" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3378" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3379" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3380" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3381" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3382" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3383" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3384" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3385" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3386" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3387" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3388" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3389" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3390" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3391" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3392" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3393" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3394" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3395" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3396" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3397" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3398" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3399" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3400" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3401" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3402" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3403" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3404" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3405" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3406" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3407" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3408" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3409" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3410" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3411" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3412" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3413" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3414" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3415" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3416" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3417" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3418" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3419" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3420" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3421" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3422" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3423" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3424" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3425" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3426" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3427" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3428" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3429" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3430" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3431" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3432" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3433" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3434" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3435" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3436" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3437" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3438" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3439" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3440" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3441" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3442" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3443" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3444" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3445" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3446" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3447" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3448" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3449" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3450" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3451" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3452" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3453" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3454" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3455" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3456" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3457" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3458" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3459" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3460" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3461" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3462" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3463" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3464" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3465" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3466" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3467" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3468" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3469" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3470" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3471" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3472" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3473" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3474" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3475" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3476" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3477" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3478" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3479" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3480" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3481" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3482" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3483" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3484" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3485" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3486" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3487" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3488" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3489" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3490" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3491" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3492" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3493" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3494" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3495" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3496" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3497" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3498" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3499" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3500" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3501" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3502" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3503" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3504" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3505" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3506" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3507" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3508" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3509" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3510" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3511" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3512" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3513" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3514" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3515" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3516" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3517" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3518" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3519" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3520" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3521" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3522" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3523" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3524" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3525" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3526" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3527" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3528" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3529" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3530" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3531" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3532" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3533" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3534" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3535" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3536" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3537" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3538" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3539" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3540" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3541" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3542" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3543" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3544" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3545" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3546" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3547" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3548" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3549" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3550" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3551" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3552" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3553" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3554" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3555" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3556" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3557" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3558" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3559" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3560" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3561" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3562" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3563" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3564" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3565" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3566" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3567" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3568" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3569" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3570" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3571" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3572" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3573" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3574" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3575" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3576" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3577" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3578" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3579" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3580" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3581" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3582" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3583" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3584" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3585" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3586" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3587" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3588" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3589" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3590" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3591" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3592" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3593" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3594" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3595" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3596" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3597" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3598" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3599" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3600" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3601" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3602" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3603" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3604" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3605" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3606" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3607" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3608" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3609" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3610" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3611" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3612" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3613" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3614" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3615" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3616" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3617" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3618" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3619" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3620" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3621" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3622" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3623" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3624" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3625" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3626" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3627" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3628" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3629" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3630" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3631" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3632" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3633" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3634" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3635" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3636" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3637" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3638" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3639" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3640" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3641" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3642" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3643" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3644" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3645" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3646" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3647" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3648" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3649" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3650" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3651" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3652" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3653" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3654" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3655" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3656" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3657" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3658" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3659" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3660" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3661" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3662" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3663" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3664" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3665" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3666" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3667" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3668" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3669" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3670" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3671" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3672" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3673" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3674" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3675" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3676" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3677" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3678" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3679" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3680" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3681" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3682" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3683" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3684" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3685" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3686" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3687" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3688" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3689" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3690" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3691" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3692" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3693" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3694" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3695" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3696" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3697" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3698" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3699" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3700" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3701" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3702" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3703" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3704" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3705" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3706" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3707" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3708" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3709" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3710" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3711" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3712" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3713" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3714" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3715" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3716" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3717" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3718" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3719" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3720" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3721" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3722" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3723" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3724" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3725" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3726" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3727" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3728" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3729" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3730" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3731" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3732" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3733" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3734" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3735" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3736" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3737" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3738" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3739" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3740" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3741" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3742" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3743" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3744" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3745" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3746" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3747" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3748" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3749" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3750" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3751" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3752" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3753" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3754" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3755" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3756" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3757" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3758" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3759" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3760" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3761" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3762" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3763" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3764" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3765" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3766" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3767" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3768" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3769" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3770" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3771" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3772" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3773" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3774" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3775" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3776" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3777" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3778" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3779" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3780" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3781" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3782" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3783" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3784" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3785" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3786" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3787" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3788" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3789" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3790" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3791" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3792" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3793" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3794" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3795" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3796" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3797" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3798" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3799" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3800" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3801" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3802" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3803" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3804" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3805" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3806" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3807" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3808" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3809" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3810" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3811" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3812" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3813" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3814" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3815" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3816" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3817" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3818" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3819" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3820" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3821" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3822" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3823" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3824" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3825" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3826" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3827" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3828" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3829" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3830" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3831" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3832" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3833" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3834" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3835" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3836" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3837" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3838" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3839" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3840" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3841" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3842" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3843" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3844" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3845" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3846" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3847" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3848" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3849" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3850" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3851" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3852" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3853" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3854" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3855" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3856" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3857" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3858" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3859" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3860" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3861" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3862" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3863" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3864" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3865" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3866" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3867" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3868" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3869" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3870" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3871" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3872" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3873" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3874" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3875" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3876" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3877" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3878" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3879" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3880" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3881" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3882" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3883" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3884" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3885" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3886" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3887" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3888" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3889" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3890" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3891" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3892" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3893" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3894" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3895" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3896" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3897" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3898" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3899" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3900" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3901" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3902" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3903" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3904" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3905" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3906" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3907" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3908" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3909" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3910" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3911" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3912" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3913" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3914" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3915" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3916" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3917" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3918" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3919" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3920" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3921" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3922" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3923" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3924" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3925" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3926" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3927" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3928" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3929" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3930" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3931" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3932" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3933" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3934" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3935" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3936" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3937" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3938" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3939" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3940" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3941" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3942" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3943" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3944" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3945" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3946" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3947" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3948" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3949" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3950" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3951" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3952" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3953" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3954" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3955" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3956" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3957" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3958" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3959" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3960" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3961" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3962" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3963" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3964" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3965" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3966" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3967" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3968" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3969" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3970" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3971" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3972" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3973" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3974" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3975" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3976" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3977" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3978" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3979" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3980" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3981" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3982" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3983" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3984" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3985" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3986" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3987" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3988" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3989" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3990" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3991" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3992" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3993" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3994" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3995" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3996" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3997" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3998" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="3999" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4000" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4001" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4002" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4003" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4004" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4005" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4006" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4007" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4008" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4009" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4010" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4011" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4012" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4013" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4014" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4015" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4016" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4017" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4018" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4019" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4020" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4021" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4022" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4023" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4024" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4025" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4026" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4027" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4028" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4029" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4030" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4031" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4032" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4033" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4034" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4035" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4036" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4037" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4038" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4039" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4040" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4041" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4042" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4043" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4044" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4045" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4046" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4047" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4048" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4049" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4050" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4051" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4052" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4053" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4054" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4055" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4056" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4057" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4058" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4059" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4060" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4061" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4062" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4063" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4064" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4065" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4066" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4067" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4068" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4069" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4070" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4071" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4072" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4073" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4074" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4075" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4076" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4077" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4078" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4079" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4080" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4081" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4082" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4083" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4084" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4085" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4086" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4087" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4088" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4089" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4090" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4091" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4092" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4093" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4094" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4095" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4096" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4097" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4098" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4099" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4100" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4101" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4102" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4103" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4104" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4105" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4106" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4107" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4108" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4109" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4110" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4111" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4112" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4123" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4124" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4125" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4126" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4127" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4128" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4129" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4130" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4131" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4132" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4133" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4134" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4135" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4136" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4137" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4138" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4139" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4140" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4141" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4142" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4143" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4144" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="4145" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:C4145" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}"/>
+  <autoFilter ref="A1:C4145" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Mio Matic"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Products family (1).xlsx
+++ b/Products family (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beyondbelievers-my.sharepoint.com/personal/k_saguem_z_systems/Documents/Bureau/Rehab app ( planner) - Copie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D04ECAF1-36A5-4BEA-8228-97D51AD09D6B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7BF3064-B510-4204-A5AE-77FB5322B3A7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
+    <workbookView minimized="1" xWindow="6456" yWindow="4056" windowWidth="17280" windowHeight="8880" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
   </bookViews>
   <sheets>
     <sheet name="Famille-Produit" sheetId="1" r:id="rId1"/>
@@ -146,6 +146,11 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>ART01505</v>
+          </cell>
+        </row>
         <row r="34">
           <cell r="A34" t="str">
             <v>ART00049</v>
@@ -4135,8 +4140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:C4145"/>
+  <dimension ref="A1:C460"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
@@ -4156,7 +4160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str">
         <f>[1]Products!A930</f>
         <v>CF35250</v>
@@ -4170,7 +4174,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
         <f>[1]Products!A940</f>
         <v>ART00968</v>
@@ -4184,7 +4188,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
         <f>[1]Products!A1125</f>
         <v>CF35266</v>
@@ -4198,7 +4202,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="str">
         <f>[1]Products!A1126</f>
         <v>CF35267</v>
@@ -4212,7 +4216,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="str">
         <f>[1]Products!A1173</f>
         <v>CF35298</v>
@@ -4226,7 +4230,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
         <f>[1]Products!A1229</f>
         <v>CF35516</v>
@@ -4240,7 +4244,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="str">
         <f>[1]Products!A1257</f>
         <v>CF35517</v>
@@ -4254,7 +4258,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="str">
         <f>[1]Products!A1355</f>
         <v>CF35518</v>
@@ -4268,7 +4272,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="str">
         <f>[1]Products!A1422</f>
         <v>ART00221</v>
@@ -4282,7 +4286,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
         <f>[1]Products!A1423</f>
         <v>ART00222</v>
@@ -4296,7 +4300,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <f>[1]Products!A1424</f>
         <v>ART00223</v>
@@ -4310,7 +4314,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <f>[1]Products!A1425</f>
         <v>ART00224</v>
@@ -4324,7 +4328,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <f>[1]Products!A1426</f>
         <v>ART00225</v>
@@ -4338,7 +4342,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <f>[1]Products!A1427</f>
         <v>ART00226</v>
@@ -4352,7 +4356,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f>[1]Products!A1428</f>
         <v>ART00227</v>
@@ -4366,7 +4370,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="str">
         <f>[1]Products!A1429</f>
         <v>ART00228</v>
@@ -4380,7 +4384,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="str">
         <f>[1]Products!A1430</f>
         <v>ART00229</v>
@@ -4394,7 +4398,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="str">
         <f>[1]Products!A1431</f>
         <v>ART00230</v>
@@ -4408,7 +4412,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="str">
         <f>[1]Products!A1432</f>
         <v>ART00232</v>
@@ -4422,7 +4426,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="str">
         <f>[1]Products!A1487</f>
         <v>ART00294</v>
@@ -4436,7 +4440,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="str">
         <f>[1]Products!A1488</f>
         <v>ART00295</v>
@@ -4450,7 +4454,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="str">
         <f>[1]Products!A1539</f>
         <v>ART00356</v>
@@ -4464,7 +4468,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="str">
         <f>[1]Products!A1540</f>
         <v>ART00357</v>
@@ -4478,7 +4482,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="str">
         <f>[1]Products!A1652</f>
         <v>ART00525</v>
@@ -4492,7 +4496,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="str">
         <f>[1]Products!A1684</f>
         <v>ART00523</v>
@@ -4506,7 +4510,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="str">
         <f>[1]Products!A1685</f>
         <v>ART00524</v>
@@ -4520,7 +4524,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="str">
         <f>[1]Products!A1689</f>
         <v>ART00530</v>
@@ -4534,7 +4538,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="str">
         <f>[1]Products!A1690</f>
         <v>ART00531</v>
@@ -4548,7 +4552,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="str">
         <f>[1]Products!A1691</f>
         <v>ART00532</v>
@@ -4562,7 +4566,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="str">
         <f>[1]Products!A1833</f>
         <v>ART00682</v>
@@ -4576,7 +4580,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="str">
         <f>[1]Products!A1898</f>
         <v>ART00744</v>
@@ -4590,7 +4594,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="str">
         <f>[1]Products!A1899</f>
         <v>ART00745</v>
@@ -4604,7 +4608,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="str">
         <f>[1]Products!A1956</f>
         <v>ART00810</v>
@@ -4618,7 +4622,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="str">
         <f>[1]Products!A1957</f>
         <v>ART00811</v>
@@ -4632,7 +4636,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="str">
         <f>[1]Products!A2077</f>
         <v>ART00953</v>
@@ -4646,7 +4650,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="str">
         <f>[1]Products!A2095</f>
         <v>ART00969</v>
@@ -4660,7 +4664,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="str">
         <f>[1]Products!A2105</f>
         <v>ART00979</v>
@@ -4674,7 +4678,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="str">
         <f>[1]Products!A2280</f>
         <v>ART01161</v>
@@ -4688,7 +4692,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="str">
         <f>[1]Products!A2562</f>
         <v>ART01454</v>
@@ -4702,7 +4706,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="str">
         <f>[1]Products!A2583</f>
         <v>ART01475</v>
@@ -4716,7 +4720,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="str">
         <f>[1]Products!A2584</f>
         <v>ART01476</v>
@@ -4730,7 +4734,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="str">
         <f>[1]Products!A3230</f>
         <v>CF35524</v>
@@ -4744,7 +4748,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="str">
         <f>[1]Products!A3232</f>
         <v>CF35525</v>
@@ -4758,7 +4762,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="str">
         <f>[1]Products!A3233</f>
         <v>CF35529</v>
@@ -4772,7 +4776,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="str">
         <f>[1]Products!A3234</f>
         <v>CF35531</v>
@@ -4786,7 +4790,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="str">
         <f>[1]Products!A3518</f>
         <v>ART03301</v>
@@ -4800,7 +4804,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="str">
         <f>[1]Products!A3522</f>
         <v>ART03300</v>
@@ -4814,7 +4818,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="str">
         <f>[1]Products!A3523</f>
         <v>ART03302</v>
@@ -4828,7 +4832,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="str">
         <f>[1]Products!A4071</f>
         <v>CF35172</v>
@@ -4842,7 +4846,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="str">
         <f>[1]Products!A4075</f>
         <v>CF35217</v>
@@ -4856,7 +4860,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="str">
         <f>[1]Products!A4076</f>
         <v>CF35218</v>
@@ -4870,7 +4874,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="str">
         <f>[1]Products!A4077</f>
         <v>CF35219</v>
@@ -4884,7 +4888,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="str">
         <f>[1]Products!A4094</f>
         <v>CF35221</v>
@@ -4898,7 +4902,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="str">
         <f>[1]Products!A4095</f>
         <v>CF35226</v>
@@ -4912,7 +4916,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="str">
         <f>[1]Products!A4096</f>
         <v>CF35227</v>
@@ -4926,7 +4930,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="str">
         <f>[1]Products!A4097</f>
         <v>CF35235</v>
@@ -4940,7 +4944,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="str">
         <f>[1]Products!A4098</f>
         <v>CF35237</v>
@@ -4954,7 +4958,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="str">
         <f>[1]Products!A4099</f>
         <v>CF35238</v>
@@ -4968,7 +4972,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="str">
         <f>[1]Products!A4100</f>
         <v>CF35240</v>
@@ -4982,7 +4986,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="str">
         <f>[1]Products!A4101</f>
         <v>CF35241</v>
@@ -4996,7 +5000,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="str">
         <f>[1]Products!A4102</f>
         <v>CF35249</v>
@@ -5010,7 +5014,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="str">
         <f>[1]Products!A4105</f>
         <v>CF35901</v>
@@ -5024,7 +5028,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="str">
         <f>[1]Products!A4106</f>
         <v>CF35902</v>
@@ -5038,7 +5042,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="str">
         <f>[1]Products!A4107</f>
         <v>CF35903</v>
@@ -5052,7 +5056,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="str">
         <f>[1]Products!A4108</f>
         <v>CF35904</v>
@@ -5066,7 +5070,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="str">
         <f>[1]Products!A4109</f>
         <v>CF35914</v>
@@ -5080,7 +5084,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="str">
         <f>[1]Products!A4110</f>
         <v>CF35916</v>
@@ -5094,7 +5098,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="str">
         <f>[1]Products!A4178</f>
         <v>CF35208</v>
@@ -5108,7 +5112,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="str">
         <f>[1]Products!A4179</f>
         <v>CF35210</v>
@@ -5122,7 +5126,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="str">
         <f>[1]Products!A4180</f>
         <v>CF35212</v>
@@ -5136,7 +5140,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="str">
         <f>[1]Products!A4181</f>
         <v>CF35213</v>
@@ -5150,7 +5154,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="str">
         <f>[1]Products!A4183</f>
         <v>CF35900</v>
@@ -5164,7 +5168,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="str">
         <f>[1]Products!A4184</f>
         <v>CF35246</v>
@@ -5178,7 +5182,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="str">
         <f>[1]Products!A4185</f>
         <v>CF35245</v>
@@ -5192,7 +5196,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="str">
         <f>[1]Products!A4186</f>
         <v>CF35171</v>
@@ -5206,7 +5210,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="str">
         <f>[1]Products!A4187</f>
         <v>CF35198</v>
@@ -5220,7 +5224,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="str">
         <f>[1]Products!A4188</f>
         <v>CF35199</v>
@@ -5234,7 +5238,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="str">
         <f>[1]Products!A4190</f>
         <v>CF35223</v>
@@ -5248,7 +5252,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="str">
         <f>[1]Products!A4191</f>
         <v>CF35224</v>
@@ -5262,7 +5266,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="str">
         <f>[1]Products!A4192</f>
         <v>CF35225</v>
@@ -5276,7 +5280,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="str">
         <f>[1]Products!A4193</f>
         <v>CF35239</v>
@@ -5290,7 +5294,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="str">
         <f>[1]Products!A4194</f>
         <v>CF35242</v>
@@ -5304,7 +5308,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="str">
         <f>[1]Products!A4195</f>
         <v>CF35265</v>
@@ -5318,7 +5322,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="str">
         <f>[1]Products!A4196</f>
         <v>CF35530</v>
@@ -5332,7 +5336,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="str">
         <f>[1]Products!A4197</f>
         <v>CF35120</v>
@@ -5346,7 +5350,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="str">
         <f>[1]Products!A4198</f>
         <v>CF35121</v>
@@ -5360,7 +5364,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="str">
         <f>[1]Products!A4199</f>
         <v>CF35122</v>
@@ -5374,7 +5378,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="str">
         <f>[1]Products!A4200</f>
         <v>CF35178</v>
@@ -5388,7 +5392,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="str">
         <f>[1]Products!A4201</f>
         <v>CF35197</v>
@@ -5402,7 +5406,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="str">
         <f>[1]Products!A4202</f>
         <v>CF35118</v>
@@ -5416,7 +5420,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="str">
         <f>[1]Products!A4203</f>
         <v>CF35127</v>
@@ -5430,7 +5434,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="str">
         <f>[1]Products!A3631</f>
         <v>ART03422</v>
@@ -5444,7 +5448,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="str">
         <f>[1]Products!A3670</f>
         <v>ART03417</v>
@@ -5458,7 +5462,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="str">
         <f>[1]Products!A4063</f>
         <v>CF34026</v>
@@ -5472,7 +5476,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="str">
         <f>[1]Products!A4068</f>
         <v>CF34069</v>
@@ -5486,7 +5490,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="str">
         <f>[1]Products!A4070</f>
         <v>CF34070</v>
@@ -5500,7 +5504,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="str">
         <f>[1]Products!A4087</f>
         <v>CF34027</v>
@@ -5514,7 +5518,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="str">
         <f>[1]Products!A4088</f>
         <v>CF34029</v>
@@ -5528,7 +5532,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="str">
         <f>[1]Products!A4089</f>
         <v>CF34030</v>
@@ -5542,7 +5546,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="str">
         <f>[1]Products!A4090</f>
         <v>CF34046</v>
@@ -5556,7 +5560,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="str">
         <f>[1]Products!A4091</f>
         <v>CF34062</v>
@@ -5570,7 +5574,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="str">
         <f>[1]Products!A4092</f>
         <v>CF34063</v>
@@ -5584,7 +5588,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="str">
         <f>[1]Products!A4093</f>
         <v>CF34068</v>
@@ -5598,7 +5602,7 @@
         <v>The Al Itkane</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="str">
         <f>[1]Products!A1098</f>
         <v>ART03641</v>
@@ -5612,7 +5616,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="str">
         <f>[1]Products!A1099</f>
         <v>ART03642</v>
@@ -5626,7 +5630,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="str">
         <f>[1]Products!A1100</f>
         <v>ART03643</v>
@@ -5640,7 +5644,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="str">
         <f>[1]Products!A1110</f>
         <v>ART03644</v>
@@ -5654,7 +5658,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="str">
         <f>[1]Products!A1117</f>
         <v>ART03645</v>
@@ -5668,7 +5672,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="str">
         <f>[1]Products!A1118</f>
         <v>ART03646</v>
@@ -5682,7 +5686,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="str">
         <f>[1]Products!A1119</f>
         <v>ART03647</v>
@@ -5696,7 +5700,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="str">
         <f>[1]Products!A1120</f>
         <v>ART03649</v>
@@ -5710,7 +5714,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="str">
         <f>[1]Products!A1121</f>
         <v>ART03650</v>
@@ -5724,7 +5728,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="str">
         <f>[1]Products!A1122</f>
         <v>ART03651</v>
@@ -5738,7 +5742,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="str">
         <f>[1]Products!A1123</f>
         <v>ART03652</v>
@@ -5752,7 +5756,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="str">
         <f>[1]Products!A1124</f>
         <v>ART03653</v>
@@ -5766,7 +5770,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="str">
         <f>[1]Products!A1415</f>
         <v>ART03648</v>
@@ -5780,7 +5784,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="str">
         <f>[1]Products!A1416</f>
         <v>ART03663</v>
@@ -5794,7 +5798,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="str">
         <f>[1]Products!A1417</f>
         <v>ART03675</v>
@@ -5808,7 +5812,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="str">
         <f>[1]Products!A3390</f>
         <v>ART03668</v>
@@ -5822,7 +5826,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="str">
         <f>[1]Products!A3422</f>
         <v>ART03996</v>
@@ -5836,7 +5840,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="str">
         <f>[1]Products!A3469</f>
         <v>ART03670</v>
@@ -5850,7 +5854,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="str">
         <f>[1]Products!A3759</f>
         <v>ART03658</v>
@@ -5864,7 +5868,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="str">
         <f>[1]Products!A3847</f>
         <v>ART03661</v>
@@ -5878,7 +5882,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="str">
         <f>[1]Products!A3848</f>
         <v>ART03673</v>
@@ -5892,7 +5896,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="str">
         <f>[1]Products!A3881</f>
         <v>ART03654</v>
@@ -5906,7 +5910,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="str">
         <f>[1]Products!A3882</f>
         <v>ART03655</v>
@@ -5920,7 +5924,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="str">
         <f>[1]Products!A3883</f>
         <v>ART03656</v>
@@ -5934,7 +5938,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="str">
         <f>[1]Products!A3884</f>
         <v>ART03657</v>
@@ -5948,7 +5952,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="str">
         <f>[1]Products!A3885</f>
         <v>ART03659</v>
@@ -5962,7 +5966,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="str">
         <f>[1]Products!A3886</f>
         <v>ART03660</v>
@@ -5976,7 +5980,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="str">
         <f>[1]Products!A3887</f>
         <v>ART03662</v>
@@ -5990,7 +5994,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="str">
         <f>[1]Products!A3888</f>
         <v>ART03664</v>
@@ -6004,7 +6008,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="str">
         <f>[1]Products!A3889</f>
         <v>ART03665</v>
@@ -6018,7 +6022,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="str">
         <f>[1]Products!A3890</f>
         <v>ART03666</v>
@@ -6032,7 +6036,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="str">
         <f>[1]Products!A3891</f>
         <v>ART03667</v>
@@ -6046,7 +6050,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="str">
         <f>[1]Products!A3892</f>
         <v>ART03669</v>
@@ -6060,7 +6064,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="str">
         <f>[1]Products!A3893</f>
         <v>ART03671</v>
@@ -6074,7 +6078,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="str">
         <f>[1]Products!A3894</f>
         <v>ART03672</v>
@@ -6088,7 +6092,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="str">
         <f>[1]Products!A3895</f>
         <v>ART03674</v>
@@ -6102,7 +6106,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="str">
         <f>[1]Products!A3896</f>
         <v>ART03676</v>
@@ -6116,7 +6120,7 @@
         <v>Tawil</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="str">
         <f>[1]Products!A3368</f>
         <v>ART03703</v>
@@ -6130,7 +6134,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="str">
         <f>[1]Products!A3462</f>
         <v>ART03704</v>
@@ -6144,7 +6148,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="str">
         <f>[1]Products!A3998</f>
         <v>ART03705</v>
@@ -6158,7 +6162,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="str">
         <f>[1]Products!A3999</f>
         <v>ART03706</v>
@@ -6172,7 +6176,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="str">
         <f>[1]Products!A4001</f>
         <v>ART03707</v>
@@ -6186,7 +6190,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="str">
         <f>[1]Products!A4009</f>
         <v>ART03984</v>
@@ -6200,7 +6204,7 @@
         <v>TAKYS</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="str">
         <f>[1]Products!A94</f>
         <v>ART03709</v>
@@ -6214,7 +6218,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="str">
         <f>[1]Products!A100</f>
         <v>ART03711</v>
@@ -6228,7 +6232,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="str">
         <f>[1]Products!A1418</f>
         <v>ART03710</v>
@@ -6242,7 +6246,7 @@
         <v>TAJ SAHARA</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="str">
         <f>[1]Products!A2310</f>
         <v>ART01192</v>
@@ -6256,7 +6260,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="str">
         <f>[1]Products!A2311</f>
         <v>ART01193</v>
@@ -6270,7 +6274,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="str">
         <f>[1]Products!A2312</f>
         <v>ART01194</v>
@@ -6284,7 +6288,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="str">
         <f>[1]Products!A2313</f>
         <v>ART01195</v>
@@ -6298,7 +6302,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="str">
         <f>[1]Products!A4052</f>
         <v>CF33352</v>
@@ -6312,7 +6316,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="str">
         <f>[1]Products!A4053</f>
         <v>CF33353</v>
@@ -6326,7 +6330,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="str">
         <f>[1]Products!A4054</f>
         <v>CF33354</v>
@@ -6340,7 +6344,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="str">
         <f>[1]Products!A4055</f>
         <v>CF33355</v>
@@ -6354,7 +6358,7 @@
         <v>Shiwame</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="str">
         <f>[1]Products!A2499</f>
         <v>ART01389</v>
@@ -6368,7 +6372,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="str">
         <f>[1]Products!A2500</f>
         <v>ART01390</v>
@@ -6382,7 +6386,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="str">
         <f>[1]Products!A2501</f>
         <v>ART01391</v>
@@ -6396,7 +6400,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="str">
         <f>[1]Products!A2502</f>
         <v>ART01392</v>
@@ -6410,7 +6414,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="str">
         <f>[1]Products!A2758</f>
         <v>ART02965</v>
@@ -6424,7 +6428,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="str">
         <f>[1]Products!A2782</f>
         <v>ART02966</v>
@@ -6438,7 +6442,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="str">
         <f>[1]Products!A2783</f>
         <v>ART02967</v>
@@ -6452,7 +6456,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="str">
         <f>[1]Products!A2784</f>
         <v>ART02968</v>
@@ -6466,7 +6470,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="str">
         <f>[1]Products!A2785</f>
         <v>ART02969</v>
@@ -6480,7 +6484,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="str">
         <f>[1]Products!A2786</f>
         <v>ART02970</v>
@@ -6494,7 +6498,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="str">
         <f>[1]Products!A2787</f>
         <v>ART02971</v>
@@ -6508,7 +6512,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="str">
         <f>[1]Products!A3371</f>
         <v>ART03210</v>
@@ -6522,7 +6526,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="str">
         <f>[1]Products!A3372</f>
         <v>ART03211</v>
@@ -6536,7 +6540,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="str">
         <f>[1]Products!A3373</f>
         <v>ART03212</v>
@@ -6550,7 +6554,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="str">
         <f>[1]Products!A3676</f>
         <v>ART03447</v>
@@ -6564,7 +6568,7 @@
         <v>SANGO</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="str">
         <f>[1]Products!A614</f>
         <v>ART00513</v>
@@ -6578,7 +6582,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="str">
         <f>[1]Products!A1673</f>
         <v>ART00509</v>
@@ -6592,7 +6596,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="str">
         <f>[1]Products!A1675</f>
         <v>ART00512</v>
@@ -6606,7 +6610,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="str">
         <f>[1]Products!A3059</f>
         <v>ART02943</v>
@@ -6620,7 +6624,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="str">
         <f>[1]Products!A3060</f>
         <v>ART02944</v>
@@ -6634,7 +6638,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="str">
         <f>[1]Products!A3465</f>
         <v>ART03998</v>
@@ -6648,7 +6652,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="str">
         <f>[1]Products!A3475</f>
         <v>ART03999</v>
@@ -6662,7 +6666,7 @@
         <v>Prima</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="str">
         <f>[1]Products!A1028</f>
         <v>ART03315</v>
@@ -6676,7 +6680,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="str">
         <f>[1]Products!A3803</f>
         <v>ART03498</v>
@@ -6690,7 +6694,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="str">
         <f>[1]Products!A3804</f>
         <v>ART03499</v>
@@ -6704,7 +6708,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="str">
         <f>[1]Products!A3805</f>
         <v>ART03500</v>
@@ -6718,7 +6722,7 @@
         <v>Papillon Papier</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="str">
         <f>[1]Products!A289</f>
         <v>ART01381</v>
@@ -6732,7 +6736,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="str">
         <f>[1]Products!A648</f>
         <v>ART00014</v>
@@ -6746,7 +6750,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="str">
         <f>[1]Products!A685</f>
         <v>ART01873</v>
@@ -6760,7 +6764,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="str">
         <f>[1]Products!A793</f>
         <v>ART01902</v>
@@ -6774,7 +6778,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="str">
         <f>[1]Products!A2328</f>
         <v>ART01206</v>
@@ -6788,7 +6792,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="str">
         <f>[1]Products!A2329</f>
         <v>ART01210</v>
@@ -6802,7 +6806,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="str">
         <f>[1]Products!A2330</f>
         <v>ART01211</v>
@@ -6816,7 +6820,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="str">
         <f>[1]Products!A2573</f>
         <v>ART01453</v>
@@ -6830,7 +6834,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="str">
         <f>[1]Products!A2778</f>
         <v>ART02942</v>
@@ -6844,7 +6848,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="str">
         <f>[1]Products!A3180</f>
         <v>ART03164</v>
@@ -6858,7 +6862,7 @@
         <v>Nova</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="str">
         <f>[1]Products!A3356</f>
         <v>ART03189</v>
@@ -7068,7 +7072,7 @@
         <v>Mio Matic</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="str">
         <f>[1]Products!A607</f>
         <v>ART00292</v>
@@ -7082,7 +7086,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="19.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="str">
         <f>[1]Products!A915</f>
         <v>ART01960</v>
@@ -7096,7 +7100,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="str">
         <f>[1]Products!A934</f>
         <v>ART01967</v>
@@ -7110,7 +7114,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="str">
         <f>[1]Products!A955</f>
         <v>ART01963</v>
@@ -7124,7 +7128,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="str">
         <f>[1]Products!A1088</f>
         <v>ART01968</v>
@@ -7138,7 +7142,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="str">
         <f>[1]Products!A1502</f>
         <v>ART00291</v>
@@ -7152,7 +7156,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="str">
         <f>[1]Products!A2977</f>
         <v>ART00299</v>
@@ -7166,7 +7170,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="str">
         <f>[1]Products!A2978</f>
         <v>ART00300</v>
@@ -7180,7 +7184,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="str">
         <f>[1]Products!A2988</f>
         <v>ART01985</v>
@@ -7194,7 +7198,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="str">
         <f>[1]Products!A3195</f>
         <v>ART01971</v>
@@ -7208,7 +7212,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="str">
         <f>[1]Products!A3444</f>
         <v>ART03997</v>
@@ -7222,7 +7226,7 @@
         <v>Mio main (1k+500gr)</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="str">
         <f>[1]Products!A946</f>
         <v>ART01972</v>
@@ -7236,7 +7240,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="str">
         <f>[1]Products!A1017</f>
         <v>ART02032</v>
@@ -7250,7 +7254,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="str">
         <f>[1]Products!A1067</f>
         <v>ART02059</v>
@@ -7264,7 +7268,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="str">
         <f>[1]Products!A2980</f>
         <v>ART01973</v>
@@ -7278,7 +7282,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="str">
         <f>[1]Products!A2981</f>
         <v>ART01974</v>
@@ -7292,7 +7296,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="str">
         <f>[1]Products!A2986</f>
         <v>ART01981</v>
@@ -7306,7 +7310,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="str">
         <f>[1]Products!A2987</f>
         <v>ART01982</v>
@@ -7320,7 +7324,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="str">
         <f>[1]Products!A2997</f>
         <v>ART02027</v>
@@ -7334,7 +7338,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="str">
         <f>[1]Products!A3000</f>
         <v>ART02701</v>
@@ -7348,7 +7352,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="str">
         <f>[1]Products!A3001</f>
         <v>ART02702</v>
@@ -7362,7 +7366,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="str">
         <f>[1]Products!A3002</f>
         <v>ART02703</v>
@@ -7376,7 +7380,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="str">
         <f>[1]Products!A3003</f>
         <v>ART02704</v>
@@ -7390,7 +7394,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="str">
         <f>[1]Products!A3004</f>
         <v>ART02705</v>
@@ -7404,7 +7408,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="str">
         <f>[1]Products!A3005</f>
         <v>ART02706</v>
@@ -7418,7 +7422,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="str">
         <f>[1]Products!A3006</f>
         <v>ART02707</v>
@@ -7432,7 +7436,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="str">
         <f>[1]Products!A3007</f>
         <v>ART02708</v>
@@ -7446,7 +7450,7 @@
         <v>Mio Liquid Vaisselle</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="str">
         <f>[1]Products!A944</f>
         <v>ART02710</v>
@@ -7460,7 +7464,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="str">
         <f>[1]Products!A945</f>
         <v>ART02711</v>
@@ -7474,7 +7478,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="str">
         <f>[1]Products!A1012</f>
         <v>ART02712</v>
@@ -7488,7 +7492,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="str">
         <f>[1]Products!A2930</f>
         <v>ART02713</v>
@@ -7502,7 +7506,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="str">
         <f>[1]Products!A2931</f>
         <v>ART02714</v>
@@ -7516,7 +7520,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="str">
         <f>[1]Products!A2976</f>
         <v>ART00297</v>
@@ -7530,7 +7534,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="str">
         <f>[1]Products!A2992</f>
         <v>ART01989</v>
@@ -7544,7 +7548,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="str">
         <f>[1]Products!A2993</f>
         <v>ART01990</v>
@@ -7558,7 +7562,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="str">
         <f>[1]Products!A3008</f>
         <v>ART02709</v>
@@ -7572,7 +7576,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="str">
         <f>[1]Products!A3009</f>
         <v>ART02715</v>
@@ -7586,7 +7590,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="str">
         <f>[1]Products!A3010</f>
         <v>ART02716</v>
@@ -7600,7 +7604,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="str">
         <f>[1]Products!A3011</f>
         <v>ART02717</v>
@@ -7614,7 +7618,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="str">
         <f>[1]Products!A3025</f>
         <v>ART01991</v>
@@ -7628,7 +7632,7 @@
         <v>Mio Javel</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="str">
         <f>[1]Products!A201</f>
         <v>ART00103</v>
@@ -7642,7 +7646,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="str">
         <f>[1]Products!A283</f>
         <v>ART00301</v>
@@ -7656,7 +7660,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="str">
         <f>[1]Products!A362</f>
         <v>ART00134</v>
@@ -7670,7 +7674,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="str">
         <f>[1]Products!A421</f>
         <v>ART00333</v>
@@ -7684,7 +7688,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="str">
         <f>[1]Products!A479</f>
         <v>ART00186</v>
@@ -7698,7 +7702,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="str">
         <f>[1]Products!A1137</f>
         <v>ART00013</v>
@@ -7712,7 +7716,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="str">
         <f>[1]Products!A1199</f>
         <v>ART02125</v>
@@ -7726,7 +7730,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="str">
         <f>[1]Products!A1826</f>
         <v>ART00675</v>
@@ -7740,7 +7744,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="str">
         <f>[1]Products!A2001</f>
         <v>ART00857</v>
@@ -7754,7 +7758,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="str">
         <f>[1]Products!A2688</f>
         <v>ART02300</v>
@@ -7768,7 +7772,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="str">
         <f>[1]Products!A2689</f>
         <v>ART02140</v>
@@ -7782,7 +7786,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="str">
         <f>[1]Products!A2788</f>
         <v>ART02974</v>
@@ -7796,7 +7800,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="str">
         <f>[1]Products!A2835</f>
         <v>ART02973</v>
@@ -7810,7 +7814,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="str">
         <f>[1]Products!A3021</f>
         <v>ART03989</v>
@@ -7824,7 +7828,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="str">
         <f>[1]Products!A3045</f>
         <v>ART03988</v>
@@ -7838,7 +7842,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="str">
         <f>[1]Products!A3176</f>
         <v>ART02972</v>
@@ -7852,7 +7856,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="str">
         <f>[1]Products!A3397</f>
         <v>ART03213</v>
@@ -7866,7 +7870,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="str">
         <f>[1]Products!A3398</f>
         <v>ART03214</v>
@@ -7880,7 +7884,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="str">
         <f>[1]Products!A4046</f>
         <v>ART03986</v>
@@ -7894,7 +7898,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="str">
         <f>[1]Products!A4074</f>
         <v>ART03987</v>
@@ -7908,7 +7912,7 @@
         <v>Mia</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="str">
         <f>[1]Products!A4170</f>
         <v>ART04049</v>
@@ -7922,7 +7926,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="str">
         <f>[1]Products!A4171</f>
         <v>ART04050</v>
@@ -7936,7 +7940,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="str">
         <f>[1]Products!A4172</f>
         <v>ART04051</v>
@@ -7950,7 +7954,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="str">
         <f>[1]Products!A4173</f>
         <v>ART04053</v>
@@ -7964,7 +7968,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="str">
         <f>[1]Products!A4174</f>
         <v>ART04052</v>
@@ -7978,7 +7982,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="str">
         <f>[1]Products!A4175</f>
         <v>ART04054</v>
@@ -7992,7 +7996,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="str">
         <f>[1]Products!A4176</f>
         <v>ART04055</v>
@@ -8006,7 +8010,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="str">
         <f>[1]Products!A4177</f>
         <v>ART04056</v>
@@ -8020,7 +8024,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="str">
         <f>[1]Products!A4189</f>
         <v>ART04048</v>
@@ -8034,7 +8038,7 @@
         <v>Maresol</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="str">
         <f>[1]Products!A3961</f>
         <v>ART03779</v>
@@ -8048,7 +8052,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="str">
         <f>[1]Products!A3975</f>
         <v>ART03780</v>
@@ -8062,7 +8066,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="str">
         <f>[1]Products!A3976</f>
         <v>ART03781</v>
@@ -8076,7 +8080,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="str">
         <f>[1]Products!A3977</f>
         <v>ART03782</v>
@@ -8090,7 +8094,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="str">
         <f>[1]Products!A3978</f>
         <v>ART03783</v>
@@ -8104,7 +8108,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="str">
         <f>[1]Products!A3979</f>
         <v>ART03784</v>
@@ -8118,7 +8122,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="str">
         <f>[1]Products!A3980</f>
         <v>ART03785</v>
@@ -8132,7 +8136,7 @@
         <v>Kelloggs</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="str">
         <f>[1]Products!A611</f>
         <v>ART03604</v>
@@ -8146,7 +8150,7 @@
         <v>Douceur</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="str">
         <f>[1]Products!A2776</f>
         <v>ART03603</v>
@@ -8160,7 +8164,7 @@
         <v>Douceur</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="str">
         <f>[1]Products!A320</f>
         <v>ART01203</v>
@@ -8174,7 +8178,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="str">
         <f>[1]Products!A447</f>
         <v>ART00956</v>
@@ -8188,7 +8192,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="str">
         <f>[1]Products!A629</f>
         <v>ART00009</v>
@@ -8202,7 +8206,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="str">
         <f>[1]Products!A647</f>
         <v>ART00008</v>
@@ -8216,7 +8220,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="str">
         <f>[1]Products!A707</f>
         <v>ART00007</v>
@@ -8230,7 +8234,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="str">
         <f>[1]Products!A708</f>
         <v>ART00011</v>
@@ -8244,7 +8248,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="str">
         <f>[1]Products!A779</f>
         <v>ART01130</v>
@@ -8258,7 +8262,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="str">
         <f>[1]Products!A1102</f>
         <v>ART00010</v>
@@ -8272,7 +8276,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="str">
         <f>[1]Products!A1588</f>
         <v>ART00409</v>
@@ -8286,7 +8290,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="str">
         <f>[1]Products!A1589</f>
         <v>ART00410</v>
@@ -8300,7 +8304,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="str">
         <f>[1]Products!A2084</f>
         <v>ART00955</v>
@@ -8314,7 +8318,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="str">
         <f>[1]Products!A2265</f>
         <v>ART01131</v>
@@ -8328,7 +8332,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="str">
         <f>[1]Products!A2319</f>
         <v>ART01201</v>
@@ -8342,7 +8346,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="str">
         <f>[1]Products!A2320</f>
         <v>ART01202</v>
@@ -8356,7 +8360,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="str">
         <f>[1]Products!A2321</f>
         <v>ART01204</v>
@@ -8370,7 +8374,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="str">
         <f>[1]Products!A2322</f>
         <v>ART01205</v>
@@ -8384,7 +8388,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="str">
         <f>[1]Products!A2430</f>
         <v>ART01311</v>
@@ -8398,7 +8402,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="str">
         <f>[1]Products!A2508</f>
         <v>ART01398</v>
@@ -8412,7 +8416,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="str">
         <f>[1]Products!A2509</f>
         <v>ART01399</v>
@@ -8426,7 +8430,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="str">
         <f>[1]Products!A2510</f>
         <v>ART01401</v>
@@ -8440,7 +8444,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="str">
         <f>[1]Products!A2514</f>
         <v>ART01402</v>
@@ -8454,7 +8458,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="str">
         <f>[1]Products!A2557</f>
         <v>ART01448</v>
@@ -8468,7 +8472,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="str">
         <f>[1]Products!A2759</f>
         <v>ART02951</v>
@@ -8482,7 +8486,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="str">
         <f>[1]Products!A2760</f>
         <v>ART02953</v>
@@ -8496,7 +8500,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="str">
         <f>[1]Products!A2761</f>
         <v>ART02952</v>
@@ -8510,7 +8514,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="str">
         <f>[1]Products!A2762</f>
         <v>ART02950</v>
@@ -8524,7 +8528,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="str">
         <f>[1]Products!A2769</f>
         <v>ART02960</v>
@@ -8538,7 +8542,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="str">
         <f>[1]Products!A2770</f>
         <v>ART02949</v>
@@ -8552,7 +8556,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="str">
         <f>[1]Products!A2771</f>
         <v>ART02962</v>
@@ -8566,7 +8570,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="str">
         <f>[1]Products!A2773</f>
         <v>ART02963</v>
@@ -8580,7 +8584,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="str">
         <f>[1]Products!A2781</f>
         <v>ART02961</v>
@@ -8594,7 +8598,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="str">
         <f>[1]Products!A2812</f>
         <v>ART02983</v>
@@ -8608,7 +8612,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="str">
         <f>[1]Products!A2901</f>
         <v>ART02959</v>
@@ -8622,7 +8626,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="str">
         <f>[1]Products!A3114</f>
         <v>ART03193</v>
@@ -8636,7 +8640,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="str">
         <f>[1]Products!A3116</f>
         <v>ART03203</v>
@@ -8650,7 +8654,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="str">
         <f>[1]Products!A3117</f>
         <v>ART03204</v>
@@ -8664,7 +8668,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="str">
         <f>[1]Products!A3118</f>
         <v>ART03205</v>
@@ -8678,7 +8682,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="str">
         <f>[1]Products!A3119</f>
         <v>ART03180</v>
@@ -8692,7 +8696,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="str">
         <f>[1]Products!A3171</f>
         <v>ART03163</v>
@@ -8706,7 +8710,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="str">
         <f>[1]Products!A3357</f>
         <v>ART03192</v>
@@ -8720,7 +8724,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="str">
         <f>[1]Products!A3381</f>
         <v>ART03207</v>
@@ -8734,7 +8738,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="str">
         <f>[1]Products!A3382</f>
         <v>ART03208</v>
@@ -8748,7 +8752,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="str">
         <f>[1]Products!A3383</f>
         <v>ART03209</v>
@@ -8762,7 +8766,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="str">
         <f>[1]Products!A3410</f>
         <v>ART03239</v>
@@ -8776,7 +8780,7 @@
         <v>Dalaa VP / Baqqal / RP</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="str">
         <f>[1]Products!A295</f>
         <v>ART01673</v>
@@ -8790,7 +8794,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="str">
         <f>[1]Products!A298</f>
         <v>ART01674</v>
@@ -8804,7 +8808,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="str">
         <f>[1]Products!A299</f>
         <v>ART01671</v>
@@ -8818,7 +8822,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="str">
         <f>[1]Products!A321</f>
         <v>ART01672</v>
@@ -8832,7 +8836,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="str">
         <f>[1]Products!A322</f>
         <v>ART01675</v>
@@ -8846,7 +8850,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="str">
         <f>[1]Products!A2422</f>
         <v>ART01304</v>
@@ -8860,7 +8864,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="str">
         <f>[1]Products!A2423</f>
         <v>ART01305</v>
@@ -8874,7 +8878,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="str">
         <f>[1]Products!A2424</f>
         <v>ART01306</v>
@@ -8888,7 +8892,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="str">
         <f>[1]Products!A2426</f>
         <v>ART01307</v>
@@ -8902,7 +8906,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="str">
         <f>[1]Products!A2427</f>
         <v>ART01308</v>
@@ -8916,7 +8920,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="str">
         <f>[1]Products!A2764</f>
         <v>ART02946</v>
@@ -8930,7 +8934,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="str">
         <f>[1]Products!A2765</f>
         <v>ART02947</v>
@@ -8944,7 +8948,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="str">
         <f>[1]Products!A2766</f>
         <v>ART02948</v>
@@ -8958,7 +8962,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="str">
         <f>[1]Products!A2777</f>
         <v>ART02945</v>
@@ -8972,7 +8976,7 @@
         <v>Calin VP</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="str">
         <f>[1]Products!A34</f>
         <v>ART00049</v>
@@ -8986,7 +8990,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="str">
         <f>[1]Products!A35</f>
         <v>ART00052</v>
@@ -9000,7 +9004,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="str">
         <f>[1]Products!A47</f>
         <v>ART00050</v>
@@ -9014,7 +9018,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="str">
         <f>[1]Products!A531</f>
         <v>ART00051</v>
@@ -9028,7 +9032,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="str">
         <f>[1]Products!A2437</f>
         <v>ART01318</v>
@@ -9042,7 +9046,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="str">
         <f>[1]Products!A2443</f>
         <v>ART01326</v>
@@ -9056,7 +9060,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="str">
         <f>[1]Products!A2444</f>
         <v>ART01327</v>
@@ -9070,7 +9074,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="str">
         <f>[1]Products!A2445</f>
         <v>ART01328</v>
@@ -9084,7 +9088,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="str">
         <f>[1]Products!A2491</f>
         <v>ART01375</v>
@@ -9098,7 +9102,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="str">
         <f>[1]Products!A2492</f>
         <v>ART01376</v>
@@ -9112,7 +9116,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="str">
         <f>[1]Products!A2493</f>
         <v>ART01377</v>
@@ -9126,7 +9130,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="str">
         <f>[1]Products!A2494</f>
         <v>ART01378</v>
@@ -9140,7 +9144,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="str">
         <f>[1]Products!A2495</f>
         <v>ART01379</v>
@@ -9154,7 +9158,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="str">
         <f>[1]Products!A2496</f>
         <v>ART01380</v>
@@ -9168,7 +9172,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="str">
         <f>[1]Products!A3115</f>
         <v>ART00053</v>
@@ -9182,7 +9186,7 @@
         <v>Calin RP</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="str">
         <f>[1]Products!A3950</f>
         <v>ART03744</v>
@@ -9196,7 +9200,7 @@
         <v>Blandoux</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="str">
         <f>[1]Products!A202</f>
         <v>ART01618</v>
@@ -9210,7 +9214,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="str">
         <f>[1]Products!A203</f>
         <v>ART01616</v>
@@ -9224,7 +9228,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="str">
         <f>[1]Products!A237</f>
         <v>ART01617</v>
@@ -9238,7 +9242,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="str">
         <f>[1]Products!A240</f>
         <v>ART01615</v>
@@ -9252,7 +9256,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="str">
         <f>[1]Products!A290</f>
         <v>ART00367</v>
@@ -9266,7 +9270,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="str">
         <f>[1]Products!A301</f>
         <v>ART01678</v>
@@ -9280,7 +9284,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="str">
         <f>[1]Products!A415</f>
         <v>ART00516</v>
@@ -9294,7 +9298,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="str">
         <f>[1]Products!A1309</f>
         <v>ART00369</v>
@@ -9308,7 +9312,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="str">
         <f>[1]Products!A1362</f>
         <v>ART02277</v>
@@ -9322,7 +9326,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="str">
         <f>[1]Products!A1548</f>
         <v>ART00365</v>
@@ -9336,7 +9340,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="str">
         <f>[1]Products!A1549</f>
         <v>ART00366</v>
@@ -9350,7 +9354,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="str">
         <f>[1]Products!A1550</f>
         <v>ART00368</v>
@@ -9364,7 +9368,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="str">
         <f>[1]Products!A1551</f>
         <v>ART00370</v>
@@ -9378,7 +9382,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="str">
         <f>[1]Products!A1552</f>
         <v>ART00371</v>
@@ -9392,7 +9396,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="str">
         <f>[1]Products!A1553</f>
         <v>ART00372</v>
@@ -9406,7 +9410,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="str">
         <f>[1]Products!A1554</f>
         <v>ART00373</v>
@@ -9420,7 +9424,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="str">
         <f>[1]Products!A1555</f>
         <v>ART00374</v>
@@ -9434,7 +9438,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="str">
         <f>[1]Products!A1676</f>
         <v>ART00514</v>
@@ -9448,7 +9452,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="str">
         <f>[1]Products!A1677</f>
         <v>ART00515</v>
@@ -9462,7 +9466,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="str">
         <f>[1]Products!A1678</f>
         <v>ART00517</v>
@@ -9476,7 +9480,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="str">
         <f>[1]Products!A1692</f>
         <v>ART00533</v>
@@ -9490,7 +9494,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="str">
         <f>[1]Products!A1708</f>
         <v>ART00546</v>
@@ -9504,7 +9508,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="str">
         <f>[1]Products!A1709</f>
         <v>ART00547</v>
@@ -9518,7 +9522,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="str">
         <f>[1]Products!A1954</f>
         <v>ART00807</v>
@@ -9532,7 +9536,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="str">
         <f>[1]Products!A3098</f>
         <v>ART03148</v>
@@ -9546,7 +9550,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="str">
         <f>[1]Products!A3245</f>
         <v>CF33017</v>
@@ -9560,7 +9564,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="str">
         <f>[1]Products!A3248</f>
         <v>CF33018</v>
@@ -9574,7 +9578,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="str">
         <f>[1]Products!A3250</f>
         <v>CF33019</v>
@@ -9588,7 +9592,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="str">
         <f>[1]Products!A3251</f>
         <v>CF33020</v>
@@ -9602,7 +9606,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="str">
         <f>[1]Products!A3254</f>
         <v>CF33000</v>
@@ -9616,7 +9620,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="str">
         <f>[1]Products!A3255</f>
         <v>CF33002</v>
@@ -9630,7 +9634,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="str">
         <f>[1]Products!A3256</f>
         <v>CF33003</v>
@@ -9644,7 +9648,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="str">
         <f>[1]Products!A3257</f>
         <v>CF33005</v>
@@ -9658,7 +9662,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="str">
         <f>[1]Products!A3258</f>
         <v>CF33006</v>
@@ -9672,7 +9676,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="str">
         <f>[1]Products!A3259</f>
         <v>CF33009</v>
@@ -9686,7 +9690,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="str">
         <f>[1]Products!A3260</f>
         <v>CF33010</v>
@@ -9700,7 +9704,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="str">
         <f>[1]Products!A3261</f>
         <v>CF33011</v>
@@ -9714,7 +9718,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="str">
         <f>[1]Products!A3262</f>
         <v>CF33013</v>
@@ -9728,7 +9732,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="str">
         <f>[1]Products!A3263</f>
         <v>CF33014</v>
@@ -9742,7 +9746,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="str">
         <f>[1]Products!A3264</f>
         <v>CF33015</v>
@@ -9756,7 +9760,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="str">
         <f>[1]Products!A3265</f>
         <v>CF33016</v>
@@ -9770,7 +9774,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="str">
         <f>[1]Products!A3266</f>
         <v>CF33021</v>
@@ -9784,7 +9788,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="str">
         <f>[1]Products!A3271</f>
         <v>CF33022</v>
@@ -9798,7 +9802,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="str">
         <f>[1]Products!A3273</f>
         <v>CF33023</v>
@@ -9812,7 +9816,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="str">
         <f>[1]Products!A3274</f>
         <v>CF33024</v>
@@ -9826,7 +9830,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="str">
         <f>[1]Products!A3275</f>
         <v>CF33025</v>
@@ -9840,7 +9844,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="str">
         <f>[1]Products!A3276</f>
         <v>CF33026</v>
@@ -9854,7 +9858,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="str">
         <f>[1]Products!A3277</f>
         <v>CF33027</v>
@@ -9868,7 +9872,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="str">
         <f>[1]Products!A3278</f>
         <v>CF33028</v>
@@ -9882,7 +9886,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="str">
         <f>[1]Products!A3279</f>
         <v>CF33029</v>
@@ -9896,7 +9900,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="str">
         <f>[1]Products!A3384</f>
         <v>CF33030</v>
@@ -9910,7 +9914,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="str">
         <f>[1]Products!A3385</f>
         <v>CF33031</v>
@@ -9924,7 +9928,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="str">
         <f>[1]Products!A3386</f>
         <v>CF33032</v>
@@ -9938,7 +9942,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="str">
         <f>[1]Products!A3387</f>
         <v>CF33033</v>
@@ -9952,7 +9956,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="str">
         <f>[1]Products!A3395</f>
         <v>CF33034</v>
@@ -9966,7 +9970,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="str">
         <f>[1]Products!A3396</f>
         <v>CF33035</v>
@@ -9980,7 +9984,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="str">
         <f>[1]Products!A3447</f>
         <v>CF33063</v>
@@ -9994,7 +9998,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="str">
         <f>[1]Products!A3586</f>
         <v>CF33071</v>
@@ -10008,7 +10012,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="str">
         <f>[1]Products!A3616</f>
         <v>CF33104</v>
@@ -10022,7 +10026,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="str">
         <f>[1]Products!A3618</f>
         <v>CF33072</v>
@@ -10036,7 +10040,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="str">
         <f>[1]Products!A3621</f>
         <v>CF33075</v>
@@ -10050,7 +10054,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="str">
         <f>[1]Products!A3626</f>
         <v>CF33076</v>
@@ -10064,7 +10068,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="str">
         <f>[1]Products!A3629</f>
         <v>CF33079</v>
@@ -10078,7 +10082,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="str">
         <f>[1]Products!A3630</f>
         <v>CF33081</v>
@@ -10092,7 +10096,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="str">
         <f>[1]Products!A3635</f>
         <v>CF33082</v>
@@ -10106,7 +10110,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="str">
         <f>[1]Products!A3636</f>
         <v>CF33083</v>
@@ -10120,7 +10124,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="str">
         <f>[1]Products!A3637</f>
         <v>CF33084</v>
@@ -10134,7 +10138,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="str">
         <f>[1]Products!A3638</f>
         <v>CF33086</v>
@@ -10148,7 +10152,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="str">
         <f>[1]Products!A3639</f>
         <v>CF33092</v>
@@ -10162,7 +10166,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="str">
         <f>[1]Products!A3641</f>
         <v>CF33097</v>
@@ -10176,7 +10180,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="str">
         <f>[1]Products!A3642</f>
         <v>CF33098</v>
@@ -10190,7 +10194,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="str">
         <f>[1]Products!A3643</f>
         <v>CF33099</v>
@@ -10204,7 +10208,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="str">
         <f>[1]Products!A3644</f>
         <v>CF33102</v>
@@ -10218,7 +10222,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="str">
         <f>[1]Products!A3645</f>
         <v>CF33105</v>
@@ -10232,7 +10236,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="str">
         <f>[1]Products!A3646</f>
         <v>CF33115</v>
@@ -10246,7 +10250,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="str">
         <f>[1]Products!A3647</f>
         <v>CF33116</v>
@@ -10260,7 +10264,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="str">
         <f>[1]Products!A3701</f>
         <v>CF33117</v>
@@ -10274,7 +10278,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="str">
         <f>[1]Products!A3702</f>
         <v>CF33125</v>
@@ -10288,7 +10292,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="str">
         <f>[1]Products!A3704</f>
         <v>CF33137</v>
@@ -10302,7 +10306,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="str">
         <f>[1]Products!A4032</f>
         <v>CF33319</v>
@@ -10316,7 +10320,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="str">
         <f>[1]Products!A4111</f>
         <v>CF400978</v>
@@ -10330,7 +10334,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="str">
         <f>[1]Products!A4112</f>
         <v>CF400980</v>
@@ -10344,7 +10348,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="str">
         <f>[1]Products!A4113</f>
         <v>CF401649</v>
@@ -10358,7 +10362,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="str">
         <f>[1]Products!A4114</f>
         <v>CF401651</v>
@@ -10372,7 +10376,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="str">
         <f>[1]Products!A4117</f>
         <v>CF33080</v>
@@ -10386,7 +10390,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="str">
         <f>[1]Products!A4118</f>
         <v>CF33112</v>
@@ -10400,7 +10404,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="str">
         <f>[1]Products!A4130</f>
         <v>CF401650</v>
@@ -10414,7 +10418,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="str">
         <f>[1]Products!A4131</f>
         <v>CF401648</v>
@@ -10428,7 +10432,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="str">
         <f>[1]Products!A4132</f>
         <v>CF400981</v>
@@ -10442,7 +10446,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="str">
         <f>[1]Products!A4133</f>
         <v>CF400979</v>
@@ -10456,7 +10460,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="str">
         <f>[1]Products!A4182</f>
         <v>CF33067</v>
@@ -10470,7 +10474,7 @@
         <v>Al Itkrans + Presto</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="str">
         <f>[1]Products!A4056</f>
         <v>CF34000</v>
@@ -10483,7 +10487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="str">
         <f>[1]Products!A4057</f>
         <v>CF34001</v>
@@ -10496,7 +10500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="str">
         <f>[1]Products!A4058</f>
         <v>CF34002</v>
@@ -10509,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="str">
         <f>[1]Products!A4059</f>
         <v>CF34006</v>
@@ -10522,7 +10526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="str">
         <f>[1]Products!A4060</f>
         <v>CF34007</v>
@@ -10535,7 +10539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="str">
         <f>[1]Products!A4061</f>
         <v>CF34008</v>
@@ -10548,7 +10552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="str">
         <f>[1]Products!A4062</f>
         <v>CF34009</v>
@@ -10561,7 +10565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="2">
         <f>[1]Products!A4205</f>
         <v>0</v>
@@ -10575,3699 +10579,7 @@
         <v/>
       </c>
     </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="465" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="466" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="467" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="468" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="469" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="470" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="471" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="472" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="473" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="474" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="475" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="476" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="477" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="478" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="479" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="480" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="481" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="482" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="483" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="484" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="485" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="486" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="487" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="488" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="489" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="490" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="491" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="492" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="493" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="494" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="495" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="496" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="497" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="498" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="499" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="500" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="501" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="502" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="503" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="504" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="505" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="506" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="507" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="508" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="509" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="510" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="511" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="512" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="513" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="514" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="515" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="516" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="517" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="518" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="519" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="520" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="521" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="522" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="523" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="524" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="525" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="526" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="527" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="528" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="529" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="530" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="531" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="532" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="533" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="534" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="535" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="536" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="537" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="538" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="539" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="540" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="541" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="542" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="543" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="544" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="545" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="546" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="547" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="548" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="549" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="550" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="551" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="552" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="553" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="554" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="555" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="556" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="557" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="558" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="559" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="560" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="561" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="562" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="563" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="564" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="565" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="566" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="567" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="568" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="569" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="570" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="571" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="572" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="573" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="574" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="575" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="576" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="577" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="578" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="579" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="580" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="581" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="582" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="583" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="584" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="585" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="586" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="587" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="588" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="589" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="590" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="591" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="592" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="593" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="594" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="595" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="596" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="597" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="598" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="599" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="600" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="601" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="602" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="603" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="604" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="605" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="606" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="607" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="608" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="609" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="610" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="611" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="612" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="613" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="614" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="615" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="616" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="617" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="618" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="619" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="620" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="621" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="622" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="623" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="624" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="625" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="626" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="627" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="628" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="629" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="630" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="631" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="632" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="633" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="634" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="635" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="636" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="637" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="638" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="639" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="640" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="641" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="642" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="643" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="644" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="645" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="646" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="647" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="648" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="649" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="650" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="651" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="652" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="653" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="654" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="655" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="656" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="657" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="658" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="659" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="660" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="661" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="662" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="663" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="664" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="665" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="666" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="667" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="668" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="669" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="670" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="671" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="672" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="673" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="674" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="675" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="676" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="677" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="678" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="679" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="680" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="681" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="682" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="683" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="684" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="685" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="686" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="687" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="688" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="689" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="690" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="691" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="692" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="693" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="694" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="695" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="696" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="697" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="698" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="699" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="700" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="701" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="702" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="703" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="704" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="705" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="706" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="707" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="708" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="709" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="710" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="711" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="712" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="713" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="714" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="715" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="716" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="717" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="718" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="719" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="720" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="721" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="722" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="723" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="724" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="725" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="726" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="727" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="728" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="729" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="730" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="731" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="732" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="733" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="734" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="735" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="736" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="737" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="738" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="739" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="740" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="741" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="742" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="743" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="744" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="745" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="746" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="747" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="748" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="749" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="750" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="751" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="752" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="753" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="754" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="755" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="756" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="757" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="758" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="759" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="760" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="761" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="762" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="763" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="764" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="765" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="766" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="767" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="768" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="769" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="770" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="771" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="772" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="773" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="774" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="775" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="776" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="777" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="778" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="779" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="780" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="781" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="782" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="783" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="784" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="785" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="786" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="787" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="788" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="789" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="790" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="791" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="792" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="793" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="794" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="795" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="796" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="797" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="798" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="799" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="800" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="801" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="802" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="803" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="804" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="805" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="806" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="807" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="808" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="809" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="810" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="811" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="812" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="813" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="814" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="815" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="816" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="817" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="818" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="819" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="820" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="821" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="822" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="823" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="824" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="825" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="826" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="827" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="828" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="829" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="830" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="831" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="832" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="833" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="834" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="835" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="836" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="837" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="838" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="839" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="840" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="841" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="842" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="843" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="844" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="845" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="846" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="847" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="848" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="849" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="850" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="851" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="852" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="853" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="854" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="855" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="856" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="857" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="858" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="859" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="860" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="861" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="862" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="863" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="864" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="865" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="866" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="867" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="868" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="869" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="870" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="871" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="872" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="873" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="874" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="875" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="876" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="877" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="878" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="879" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="880" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="881" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="882" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="883" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="884" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="885" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="886" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="887" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="888" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="889" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="890" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="891" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="892" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="893" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="894" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="895" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="896" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="897" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="898" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="899" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="900" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="901" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="902" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="903" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="904" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="905" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="906" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="907" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="908" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="909" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="910" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="911" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="912" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="913" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="914" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="915" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="916" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="917" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="918" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="919" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="920" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="921" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="922" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="923" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="924" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="925" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="926" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="927" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="928" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="929" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="930" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="931" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="932" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="933" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="934" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="935" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="936" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="937" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="938" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="939" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="940" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="941" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="942" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="943" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="944" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="945" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="946" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="947" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="948" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="949" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="950" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="951" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="952" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="953" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="954" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="955" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="956" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="957" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="958" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="959" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="960" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="961" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="962" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="963" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="964" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="965" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="966" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="967" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="968" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="969" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="970" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="971" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="972" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="973" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="974" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="975" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="976" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="977" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="978" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="979" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="980" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="981" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="982" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="983" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="984" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="985" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="986" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="987" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="988" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="989" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="990" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="991" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="992" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="993" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="994" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="995" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="996" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="997" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="998" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="999" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1000" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1001" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1002" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1003" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1004" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1005" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1006" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1007" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1008" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1009" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1010" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1011" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1012" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1013" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1014" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1015" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1016" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1017" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1018" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1019" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1020" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1021" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1022" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1023" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1024" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1025" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1026" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1027" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1028" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1029" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1030" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1031" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1032" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1033" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1034" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1035" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1036" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1037" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1038" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1039" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1040" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1041" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1042" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1043" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1044" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1045" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1046" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1047" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1048" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1049" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1050" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1051" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1052" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1053" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1054" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1055" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1056" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1057" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1058" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1059" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1060" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1061" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1062" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1063" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1064" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1065" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1066" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1067" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1068" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1069" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1070" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1071" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1072" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1073" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1074" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1075" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1076" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1077" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1078" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1079" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1080" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1081" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1082" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1083" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1084" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1085" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1086" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1087" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1088" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1089" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1090" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1091" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1092" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1093" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1094" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1095" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1096" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1097" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1098" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1099" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1100" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1101" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1102" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1103" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1104" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1105" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1106" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1107" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1108" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1109" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1110" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1111" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1112" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1123" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1124" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1125" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1126" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1127" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1128" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1129" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1130" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1131" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1132" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1133" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1134" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1135" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1136" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1137" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1138" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1139" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1140" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1141" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1142" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1143" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1144" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1145" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1146" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1147" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1148" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1149" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1150" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1151" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1152" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1153" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1154" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1155" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1156" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1157" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1158" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1159" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1160" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1161" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1162" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1163" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1164" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1165" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1166" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1167" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1168" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1169" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1170" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1171" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1172" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1173" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1174" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1175" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1176" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1177" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1178" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1179" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1180" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1181" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1182" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1183" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1184" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1185" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1186" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1187" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1188" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1189" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1190" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1191" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1192" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1193" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1194" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1195" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1196" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1197" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1198" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1199" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1200" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1201" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1202" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1203" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1204" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1205" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1206" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1207" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1208" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1209" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1210" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1211" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1212" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1213" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1214" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1215" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1216" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1217" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1218" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1219" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1220" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1221" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1222" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1223" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1224" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1225" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1226" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1227" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1228" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1229" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1230" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1231" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1232" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1233" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1234" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1235" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1236" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1237" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1238" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1239" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1240" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1241" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1242" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1243" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1244" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1245" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1246" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1247" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1248" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1249" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1250" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1251" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1252" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1253" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1254" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1255" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1256" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1257" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1258" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1259" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1260" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1261" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1262" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1263" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1264" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1265" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1266" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1267" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1268" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1269" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1270" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1271" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1272" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1273" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1274" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1275" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1276" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1277" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1278" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1279" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1280" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1281" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1282" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1283" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1284" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1285" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1286" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1287" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1288" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1289" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1290" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1291" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1292" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1293" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1294" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1295" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1296" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1297" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1298" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1299" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1300" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1301" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1302" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1303" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1304" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1305" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1306" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1307" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1308" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1309" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1310" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1311" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1312" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1313" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1314" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1315" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1316" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1317" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1318" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1319" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1320" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1321" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1322" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1323" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1324" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1325" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1326" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1327" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1328" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1329" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1330" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1331" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1332" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1333" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1334" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1335" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1336" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1337" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1338" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1339" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1340" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1341" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1342" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1343" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1344" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1345" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1346" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1347" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1348" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1349" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1350" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1351" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1352" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1353" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1354" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1355" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1356" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1357" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1358" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1359" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1360" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1361" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1362" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1363" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1364" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1365" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1366" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1367" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1368" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1369" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1370" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1371" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1372" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1373" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1374" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1375" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1376" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1377" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1378" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1379" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1380" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1381" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1382" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1383" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1384" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1385" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1386" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1387" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1388" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1389" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1390" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1391" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1392" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1393" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1394" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1395" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1396" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1397" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1398" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1399" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1400" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1401" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1402" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1403" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1404" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1405" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1406" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1407" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1408" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1409" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1410" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1411" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1412" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1413" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1414" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1415" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1416" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1417" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1418" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1419" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1420" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1421" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1422" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1423" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1424" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1425" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1426" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1427" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1428" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1429" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1430" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1431" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1432" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1433" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1434" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1435" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1436" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1437" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1438" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1439" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1440" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1441" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1442" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1443" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1444" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1445" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1446" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1447" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1448" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1449" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1450" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1451" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1452" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1453" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1454" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1455" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1456" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1457" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1458" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1459" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1460" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1461" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1462" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1463" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1464" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1465" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1466" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1467" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1468" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1469" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1470" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1471" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1472" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1473" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1474" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1475" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1476" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1477" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1478" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1479" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1480" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1481" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1482" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1483" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1484" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1485" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1486" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1487" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1488" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1489" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1490" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1491" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1492" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1493" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1494" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1495" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1496" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1497" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1498" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1499" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1500" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1501" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1502" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1503" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1504" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1505" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1506" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1507" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1508" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1509" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1510" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1511" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1512" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1513" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1514" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1515" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1516" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1517" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1518" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1519" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1520" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1521" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1522" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1523" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1524" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1525" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1526" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1527" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1528" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1529" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1530" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1531" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1532" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1533" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1534" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1535" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1536" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1537" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1538" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1539" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1540" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1541" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1542" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1543" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1544" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1545" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1546" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1547" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1548" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1549" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1550" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1551" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1552" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1553" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1554" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1555" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1556" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1557" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1558" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1559" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1560" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1561" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1562" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1563" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1564" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1565" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1566" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1567" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1568" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1569" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1570" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1571" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1572" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1573" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1574" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1575" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1576" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1577" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1578" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1579" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1580" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1581" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1582" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1583" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1584" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1585" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1586" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1587" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1588" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1589" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1590" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1591" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1592" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1593" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1594" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1595" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1596" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1597" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1598" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1599" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1600" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1601" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1602" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1603" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1604" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1605" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1606" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1607" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1608" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1609" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1610" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1611" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1612" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1613" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1614" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1615" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1616" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1617" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1618" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1619" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1620" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1621" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1622" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1623" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1624" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1625" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1626" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1627" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1628" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1629" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1630" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1631" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1632" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1633" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1634" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1635" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1636" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1637" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1638" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1639" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1640" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1641" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1642" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1643" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1644" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1645" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1646" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1647" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1648" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1649" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1650" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1651" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1652" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1653" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1654" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1655" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1656" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1657" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1658" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1659" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1660" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1661" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1662" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1663" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1664" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1665" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1666" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1667" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1668" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1669" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1670" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1671" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1672" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1673" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1674" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1675" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1676" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1677" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1678" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1679" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1680" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1681" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1682" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1683" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1684" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1685" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1686" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1687" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1688" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1689" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1690" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1691" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1692" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1693" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1694" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1695" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1696" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1697" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1698" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1699" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1700" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1701" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1702" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1703" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1704" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1705" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1706" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1707" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1708" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1709" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1710" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1711" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1712" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1713" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1714" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1715" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1716" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1717" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1718" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1719" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1720" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1721" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1722" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1723" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1724" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1725" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1726" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1727" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1728" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1729" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1730" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1731" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1732" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1733" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1734" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1735" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1736" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1737" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1738" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1739" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1740" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1741" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1742" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1743" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1744" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1745" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1746" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1747" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1748" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1749" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1750" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1751" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1752" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1753" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1754" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1755" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1756" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1757" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1758" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1759" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1760" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1761" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1762" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1763" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1764" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1765" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1766" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1767" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1768" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1769" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1770" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1771" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1772" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1773" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1774" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1775" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1776" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1777" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1778" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1779" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1780" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1781" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1782" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1783" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1784" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1785" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1786" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1787" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1788" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1789" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1790" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1791" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1792" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1793" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1794" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1795" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1796" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1797" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1798" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1799" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1800" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1801" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1802" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1803" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1804" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1805" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1806" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1807" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1808" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1809" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1810" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1811" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1812" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1813" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1814" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1815" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1816" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1817" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1818" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1819" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1820" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1821" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1822" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1823" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1824" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1825" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1826" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1827" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1828" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1829" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1830" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1831" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1832" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1833" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1834" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1835" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1836" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1837" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1838" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1839" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1840" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1841" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1842" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1843" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1844" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1845" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1846" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1847" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1848" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1849" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1850" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1851" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1852" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1853" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1854" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1855" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1856" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1857" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1858" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1859" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1860" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1861" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1862" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1863" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1864" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1865" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1866" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1867" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1868" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1869" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1870" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1871" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1872" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1873" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1874" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1875" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1876" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1877" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1878" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1879" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1880" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1881" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1882" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1883" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1884" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1885" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1886" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1887" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1888" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1889" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1890" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1891" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1892" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1893" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1894" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1895" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1896" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1897" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1898" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1899" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1900" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1901" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1902" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1903" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1904" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1905" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1906" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1907" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1908" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1909" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1910" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1911" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1912" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1913" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1914" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1915" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1916" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1917" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1918" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1919" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1920" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1921" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1922" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1923" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1924" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1925" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1926" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1927" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1928" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1929" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1930" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1931" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1932" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1933" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1934" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1935" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1936" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1937" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1938" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1939" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1940" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1941" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1942" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1943" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1944" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1945" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1946" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1947" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1948" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1949" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1950" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1951" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1952" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1953" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1954" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1955" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1956" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1957" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1958" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1959" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1960" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1961" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1962" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1963" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1964" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1965" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1966" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1967" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1968" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1969" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1970" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1971" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1972" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1973" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1974" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1975" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1976" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1977" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1978" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1979" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1980" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1981" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1982" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1983" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1984" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1985" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1986" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1987" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1988" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1989" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1990" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1991" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1992" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1993" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1994" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1995" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1996" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1997" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1998" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="1999" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2000" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2001" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2002" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2003" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2004" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2005" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2006" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2007" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2008" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2009" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2010" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2011" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2012" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2013" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2014" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2015" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2016" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2017" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2018" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2019" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2020" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2021" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2022" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2023" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2024" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2025" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2026" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2027" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2028" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2029" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2030" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2031" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2032" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2033" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2034" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2035" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2036" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2037" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2038" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2039" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2040" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2041" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2042" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2043" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2044" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2045" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2046" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2047" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2048" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2049" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2050" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2051" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2052" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2053" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2054" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2055" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2056" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2057" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2058" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2059" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2060" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2061" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2062" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2063" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2064" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2065" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2066" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2067" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2068" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2069" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2070" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2071" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2072" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2073" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2074" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2075" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2076" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2077" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2078" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2079" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2080" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2081" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2082" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2083" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2084" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2085" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2086" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2087" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2088" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2089" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2090" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2091" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2092" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2093" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2094" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2095" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2096" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2097" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2098" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2099" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2100" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2101" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2102" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2103" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2104" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2105" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2106" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2107" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2108" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2109" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2110" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2111" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2112" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2123" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2124" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2125" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2126" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2127" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2128" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2129" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2130" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2131" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2132" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2133" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2134" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2135" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2136" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2137" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2138" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2139" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2140" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2141" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2142" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2143" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2144" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2145" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2146" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2147" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2148" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2149" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2150" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2151" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2152" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2153" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2154" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2155" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2156" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2157" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2158" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2159" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2160" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2161" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2162" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2163" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2164" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2165" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2166" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2167" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2168" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2169" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2170" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2171" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2172" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2173" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2174" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2175" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2176" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2177" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2178" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2179" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2180" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2181" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2182" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2183" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2184" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2185" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2186" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2187" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2188" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2189" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2190" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2191" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2192" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2193" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2194" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2195" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2196" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2197" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2198" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2199" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2200" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2201" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2202" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2203" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2204" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2205" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2206" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2207" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2208" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2209" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2210" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2211" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2212" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2213" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2214" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2215" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2216" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2217" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2218" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2219" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2220" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2221" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2222" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2223" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2224" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2225" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2226" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2227" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2228" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2229" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2230" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2231" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2232" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2233" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2234" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2235" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2236" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2237" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2238" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2239" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2240" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2241" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2242" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2243" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2244" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2245" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2246" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2247" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2248" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2249" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2250" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2251" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2252" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2253" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2254" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2255" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2256" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2257" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2258" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2259" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2260" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2261" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2262" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2263" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2264" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2265" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2266" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2267" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2268" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2269" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2270" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2271" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2272" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2273" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2274" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2275" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2276" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2277" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2278" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2279" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2280" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2281" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2282" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2283" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2284" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2285" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2286" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2287" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2288" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2289" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2290" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2291" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2292" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2293" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2294" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2295" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2296" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2297" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2298" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2299" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2300" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2301" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2302" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2303" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2304" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2305" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2306" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2307" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2308" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2309" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2310" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2311" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2312" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2313" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2314" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2315" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2316" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2317" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2318" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2319" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2320" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2321" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2322" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2323" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2324" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2325" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2326" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2327" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2328" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2329" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2330" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2331" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2332" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2333" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2334" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2335" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2336" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2337" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2338" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2339" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2340" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2341" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2342" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2343" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2344" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2345" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2346" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2347" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2348" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2349" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2350" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2351" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2352" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2353" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2354" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2355" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2356" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2357" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2358" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2359" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2360" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2361" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2362" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2363" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2364" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2365" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2366" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2367" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2368" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2369" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2370" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2371" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2372" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2373" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2374" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2375" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2376" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2377" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2378" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2379" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2380" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2381" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2382" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2383" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2384" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2385" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2386" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2387" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2388" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2389" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2390" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2391" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2392" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2393" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2394" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2395" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2396" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2397" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2398" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2399" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2400" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2401" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2402" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2403" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2404" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2405" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2406" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2407" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2408" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2409" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2410" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2411" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2412" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2413" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2414" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2415" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2416" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2417" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2418" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2419" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2420" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2421" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2422" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2423" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2424" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2425" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2426" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2427" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2428" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2429" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2430" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2431" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2432" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2433" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2434" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2435" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2436" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2437" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2438" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2439" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2440" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2441" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2442" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2443" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2444" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2445" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2446" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2447" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2448" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2449" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2450" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2451" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2452" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2453" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2454" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2455" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2456" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2457" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2458" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2459" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2460" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2461" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2462" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2463" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2464" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2465" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2466" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2467" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2468" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2469" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2470" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2471" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2472" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2473" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2474" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2475" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2476" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2477" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2478" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2479" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2480" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2481" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2482" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2483" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2484" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2485" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2486" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2487" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2488" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2489" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2490" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2491" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2492" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2493" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2494" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2495" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2496" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2497" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2498" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2499" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2500" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2501" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2502" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2503" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2504" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2505" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2506" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2507" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2508" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2509" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2510" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2511" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2512" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2513" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2514" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2515" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2516" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2517" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2518" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2519" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2520" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2521" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2522" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2523" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2524" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2525" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2526" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2527" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2528" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2529" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2530" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2531" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2532" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2533" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2534" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2535" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2536" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2537" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2538" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2539" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2540" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2541" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2542" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2543" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2544" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2545" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2546" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2547" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2548" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2549" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2550" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2551" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2552" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2553" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2554" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2555" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2556" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2557" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2558" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2559" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2560" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2561" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2562" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2563" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2564" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2565" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2566" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2567" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2568" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2569" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2570" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2571" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2572" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2573" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2574" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2575" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2576" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2577" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2578" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2579" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2580" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2581" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2582" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2583" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2584" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2585" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2586" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2587" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2588" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2589" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2590" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2591" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2592" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2593" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2594" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2595" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2596" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2597" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2598" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2599" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2600" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2601" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2602" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2603" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2604" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2605" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2606" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2607" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2608" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2609" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2610" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2611" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2612" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2613" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2614" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2615" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2616" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2617" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2618" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2619" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2620" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2621" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2622" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2623" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2624" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2625" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2626" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2627" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2628" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2629" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2630" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2631" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2632" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2633" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2634" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2635" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2636" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2637" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2638" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2639" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2640" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2641" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2642" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2643" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2644" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2645" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2646" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2647" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2648" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2649" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2650" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2651" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2652" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2653" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2654" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2655" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2656" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2657" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2658" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2659" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2660" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2661" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2662" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2663" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2664" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2665" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2666" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2667" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2668" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2669" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2670" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2671" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2672" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2673" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2674" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2675" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2676" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2677" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2678" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2679" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2680" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2681" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2682" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2683" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2684" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2685" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2686" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2687" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2688" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2689" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2690" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2691" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2692" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2693" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2694" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2695" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2696" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2697" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2698" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2699" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2700" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2701" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2702" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2703" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2704" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2705" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2706" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2707" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2708" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2709" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2710" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2711" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2712" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2713" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2714" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2715" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2716" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2717" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2718" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2719" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2720" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2721" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2722" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2723" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2724" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2725" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2726" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2727" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2728" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2729" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2730" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2731" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2732" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2733" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2734" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2735" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2736" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2737" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2738" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2739" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2740" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2741" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2742" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2743" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2744" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2745" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2746" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2747" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2748" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2749" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2750" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2751" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2752" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2753" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2754" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2755" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2756" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2757" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2758" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2759" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2760" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2761" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2762" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2763" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2764" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2765" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2766" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2767" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2768" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2769" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2770" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2771" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2772" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2773" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2774" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2775" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2776" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2777" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2778" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2779" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2780" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2781" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2782" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2783" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2784" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2785" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2786" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2787" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2788" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2789" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2790" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2791" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2792" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2793" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2794" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2795" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2796" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2797" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2798" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2799" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2800" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2801" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2802" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2803" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2804" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2805" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2806" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2807" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2808" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2809" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2810" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2811" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2812" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2813" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2814" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2815" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2816" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2817" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2818" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2819" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2820" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2821" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2822" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2823" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2824" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2825" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2826" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2827" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2828" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2829" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2830" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2831" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2832" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2833" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2834" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2835" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2836" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2837" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2838" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2839" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2840" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2841" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2842" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2843" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2844" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2845" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2846" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2847" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2848" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2849" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2850" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2851" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2852" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2853" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2854" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2855" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2856" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2857" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2858" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2859" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2860" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2861" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2862" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2863" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2864" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2865" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2866" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2867" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2868" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2869" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2870" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2871" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2872" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2873" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2874" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2875" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2876" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2877" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2878" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2879" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2880" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2881" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2882" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2883" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2884" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2885" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2886" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2887" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2888" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2889" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2890" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2891" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2892" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2893" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2894" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2895" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2896" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2897" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2898" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2899" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2900" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2901" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2902" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2903" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2904" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2905" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2906" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2907" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2908" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2909" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2910" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2911" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2912" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2913" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2914" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2915" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2916" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2917" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2918" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2919" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2920" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2921" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2922" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2923" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2924" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2925" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2926" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2927" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2928" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2929" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2930" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2931" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2932" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2933" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2934" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2935" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2936" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2937" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2938" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2939" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2940" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2941" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2942" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2943" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2944" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2945" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2946" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2947" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2948" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2949" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2950" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2951" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2952" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2953" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2954" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2955" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2956" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2957" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2958" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2959" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2960" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2961" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2962" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2963" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2964" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2965" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2966" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2967" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2968" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2969" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2970" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2971" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2972" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2973" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2974" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2975" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2976" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2977" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2978" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2979" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2980" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2981" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2982" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2983" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2984" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2985" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2986" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2987" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2988" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2989" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2990" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2991" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2992" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2993" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2994" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2995" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2996" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2997" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2998" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="2999" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3000" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3001" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3002" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3003" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3004" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3005" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3006" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3007" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3008" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3009" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3010" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3011" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3012" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3013" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3014" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3015" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3016" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3017" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3018" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3019" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3020" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3021" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3022" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3023" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3024" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3025" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3026" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3027" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3028" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3029" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3030" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3031" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3032" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3033" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3034" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3035" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3036" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3037" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3038" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3039" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3040" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3041" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3042" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3043" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3044" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3045" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3046" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3047" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3048" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3049" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3050" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3051" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3052" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3053" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3054" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3055" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3056" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3057" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3058" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3059" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3060" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3061" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3062" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3063" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3064" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3065" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3066" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3067" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3068" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3069" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3070" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3071" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3072" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3073" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3074" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3075" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3076" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3077" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3078" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3079" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3080" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3081" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3082" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3083" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3084" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3085" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3086" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3087" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3088" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3089" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3090" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3091" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3092" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3093" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3094" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3095" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3096" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3097" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3098" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3099" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3100" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3101" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3102" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3103" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3104" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3105" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3106" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3107" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3108" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3109" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3110" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3111" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3112" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3123" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3124" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3125" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3126" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3127" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3128" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3129" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3130" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3131" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3132" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3133" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3134" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3135" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3136" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3137" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3138" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3139" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3140" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3141" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3142" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3143" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3144" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3145" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3146" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3147" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3148" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3149" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3150" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3151" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3152" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3153" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3154" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3155" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3156" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3157" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3158" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3159" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3160" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3161" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3162" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3163" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3164" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3165" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3166" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3167" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3168" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3169" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3170" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3171" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3172" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3173" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3174" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3175" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3176" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3177" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3178" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3179" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3180" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3181" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3182" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3183" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3184" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3185" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3186" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3187" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3188" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3189" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3190" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3191" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3192" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3193" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3194" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3195" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3196" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3197" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3198" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3199" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3200" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3201" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3202" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3203" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3204" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3205" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3206" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3207" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3208" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3209" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3210" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3211" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3212" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3213" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3214" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3215" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3216" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3217" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3218" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3219" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3220" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3221" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3222" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3223" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3224" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3225" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3226" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3227" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3228" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3229" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3230" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3231" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3232" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3233" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3234" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3235" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3236" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3237" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3238" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3239" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3240" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3241" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3242" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3243" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3244" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3245" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3246" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3247" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3248" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3249" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3250" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3251" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3252" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3253" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3254" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3255" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3256" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3257" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3258" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3259" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3260" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3261" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3262" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3263" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3264" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3265" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3266" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3267" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3268" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3269" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3270" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3271" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3272" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3273" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3274" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3275" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3276" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3277" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3278" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3279" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3280" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3281" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3282" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3283" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3284" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3285" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3286" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3287" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3288" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3289" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3290" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3291" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3292" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3293" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3294" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3295" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3296" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3297" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3298" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3299" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3300" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3301" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3302" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3303" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3304" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3305" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3306" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3307" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3308" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3309" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3310" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3311" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3312" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3313" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3314" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3315" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3316" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3317" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3318" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3319" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3320" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3321" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3322" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3323" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3324" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3325" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3326" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3327" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3328" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3329" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3330" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3331" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3332" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3333" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3334" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3335" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3336" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3337" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3338" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3339" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3340" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3341" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3342" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3343" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3344" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3345" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3346" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3347" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3348" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3349" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3350" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3351" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3352" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3353" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3354" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3355" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3356" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3357" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3358" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3359" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3360" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3361" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3362" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3363" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3364" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3365" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3366" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3367" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3368" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3369" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3370" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3371" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3372" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3373" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3374" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3375" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3376" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3377" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3378" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3379" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3380" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3381" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3382" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3383" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3384" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3385" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3386" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3387" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3388" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3389" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3390" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3391" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3392" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3393" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3394" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3395" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3396" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3397" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3398" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3399" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3400" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3401" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3402" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3403" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3404" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3405" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3406" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3407" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3408" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3409" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3410" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3411" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3412" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3413" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3414" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3415" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3416" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3417" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3418" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3419" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3420" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3421" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3422" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3423" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3424" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3425" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3426" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3427" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3428" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3429" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3430" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3431" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3432" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3433" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3434" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3435" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3436" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3437" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3438" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3439" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3440" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3441" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3442" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3443" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3444" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3445" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3446" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3447" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3448" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3449" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3450" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3451" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3452" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3453" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3454" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3455" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3456" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3457" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3458" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3459" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3460" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3461" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3462" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3463" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3464" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3465" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3466" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3467" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3468" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3469" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3470" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3471" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3472" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3473" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3474" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3475" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3476" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3477" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3478" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3479" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3480" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3481" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3482" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3483" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3484" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3485" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3486" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3487" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3488" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3489" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3490" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3491" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3492" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3493" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3494" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3495" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3496" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3497" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3498" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3499" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3500" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3501" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3502" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3503" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3504" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3505" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3506" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3507" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3508" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3509" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3510" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3511" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3512" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3513" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3514" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3515" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3516" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3517" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3518" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3519" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3520" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3521" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3522" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3523" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3524" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3525" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3526" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3527" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3528" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3529" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3530" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3531" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3532" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3533" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3534" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3535" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3536" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3537" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3538" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3539" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3540" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3541" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3542" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3543" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3544" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3545" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3546" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3547" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3548" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3549" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3550" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3551" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3552" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3553" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3554" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3555" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3556" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3557" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3558" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3559" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3560" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3561" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3562" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3563" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3564" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3565" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3566" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3567" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3568" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3569" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3570" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3571" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3572" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3573" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3574" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3575" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3576" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3577" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3578" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3579" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3580" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3581" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3582" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3583" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3584" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3585" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3586" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3587" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3588" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3589" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3590" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3591" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3592" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3593" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3594" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3595" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3596" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3597" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3598" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3599" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3600" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3601" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3602" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3603" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3604" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3605" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3606" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3607" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3608" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3609" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3610" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3611" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3612" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3613" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3614" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3615" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3616" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3617" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3618" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3619" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3620" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3621" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3622" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3623" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3624" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3625" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3626" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3627" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3628" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3629" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3630" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3631" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3632" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3633" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3634" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3635" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3636" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3637" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3638" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3639" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3640" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3641" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3642" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3643" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3644" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3645" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3646" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3647" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3648" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3649" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3650" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3651" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3652" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3653" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3654" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3655" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3656" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3657" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3658" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3659" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3660" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3661" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3662" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3663" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3664" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3665" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3666" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3667" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3668" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3669" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3670" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3671" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3672" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3673" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3674" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3675" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3676" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3677" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3678" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3679" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3680" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3681" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3682" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3683" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3684" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3685" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3686" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3687" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3688" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3689" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3690" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3691" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3692" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3693" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3694" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3695" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3696" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3697" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3698" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3699" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3700" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3701" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3702" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3703" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3704" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3705" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3706" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3707" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3708" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3709" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3710" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3711" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3712" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3713" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3714" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3715" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3716" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3717" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3718" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3719" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3720" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3721" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3722" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3723" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3724" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3725" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3726" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3727" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3728" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3729" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3730" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3731" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3732" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3733" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3734" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3735" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3736" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3737" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3738" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3739" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3740" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3741" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3742" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3743" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3744" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3745" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3746" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3747" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3748" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3749" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3750" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3751" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3752" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3753" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3754" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3755" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3756" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3757" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3758" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3759" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3760" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3761" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3762" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3763" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3764" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3765" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3766" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3767" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3768" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3769" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3770" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3771" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3772" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3773" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3774" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3775" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3776" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3777" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3778" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3779" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3780" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3781" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3782" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3783" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3784" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3785" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3786" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3787" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3788" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3789" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3790" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3791" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3792" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3793" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3794" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3795" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3796" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3797" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3798" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3799" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3800" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3801" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3802" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3803" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3804" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3805" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3806" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3807" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3808" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3809" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3810" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3811" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3812" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3813" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3814" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3815" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3816" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3817" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3818" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3819" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3820" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3821" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3822" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3823" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3824" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3825" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3826" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3827" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3828" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3829" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3830" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3831" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3832" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3833" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3834" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3835" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3836" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3837" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3838" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3839" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3840" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3841" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3842" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3843" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3844" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3845" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3846" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3847" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3848" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3849" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3850" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3851" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3852" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3853" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3854" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3855" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3856" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3857" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3858" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3859" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3860" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3861" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3862" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3863" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3864" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3865" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3866" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3867" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3868" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3869" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3870" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3871" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3872" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3873" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3874" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3875" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3876" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3877" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3878" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3879" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3880" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3881" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3882" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3883" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3884" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3885" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3886" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3887" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3888" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3889" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3890" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3891" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3892" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3893" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3894" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3895" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3896" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3897" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3898" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3899" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3900" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3901" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3902" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3903" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3904" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3905" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3906" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3907" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3908" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3909" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3910" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3911" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3912" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3913" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3914" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3915" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3916" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3917" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3918" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3919" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3920" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3921" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3922" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3923" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3924" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3925" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3926" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3927" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3928" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3929" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3930" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3931" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3932" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3933" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3934" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3935" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3936" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3937" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3938" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3939" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3940" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3941" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3942" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3943" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3944" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3945" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3946" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3947" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3948" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3949" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3950" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3951" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3952" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3953" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3954" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3955" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3956" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3957" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3958" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3959" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3960" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3961" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3962" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3963" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3964" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3965" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3966" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3967" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3968" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3969" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3970" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3971" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3972" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3973" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3974" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3975" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3976" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3977" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3978" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3979" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3980" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3981" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3982" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3983" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3984" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3985" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3986" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3987" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3988" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3989" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3990" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3991" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3992" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3993" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3994" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3995" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3996" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3997" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3998" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="3999" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4000" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4001" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4002" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4003" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4004" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4005" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4006" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4007" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4008" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4009" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4010" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4011" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4012" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4013" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4014" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4015" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4016" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4017" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4018" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4019" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4020" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4021" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4022" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4023" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4024" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4025" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4026" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4027" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4028" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4029" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4030" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4031" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4032" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4033" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4034" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4035" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4036" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4037" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4038" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4039" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4040" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4041" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4042" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4043" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4044" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4045" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4046" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4047" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4048" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4049" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4050" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4051" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4052" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4053" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4054" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4055" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4056" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4057" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4058" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4059" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4060" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4061" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4062" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4063" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4064" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4065" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4066" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4067" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4068" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4069" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4070" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4071" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4072" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4073" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4074" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4075" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4076" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4077" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4078" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4079" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4080" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4081" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4082" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4083" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4084" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4085" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4086" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4087" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4088" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4089" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4090" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4091" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4092" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4093" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4094" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4095" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4096" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4097" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4098" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4099" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4100" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4101" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4102" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4103" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4104" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4105" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4106" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4107" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4108" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4109" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4110" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4111" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4112" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4123" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4124" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4125" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4126" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4127" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4128" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4129" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4130" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4131" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4132" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4133" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4134" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4135" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4136" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4137" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4138" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4139" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4140" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4141" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4142" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4143" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4144" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="4145" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:C4145" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Mio Matic"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Products family (1).xlsx
+++ b/Products family (1).xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beyondbelievers-my.sharepoint.com/personal/k_saguem_z_systems/Documents/Bureau/Rehab app ( planner) - Copie/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7BF3064-B510-4204-A5AE-77FB5322B3A7}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{4B768603-55D6-5F4F-9B0A-1257BA9203EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C8A78C1-4B12-468E-A62C-475F2D7A058F}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6456" yWindow="4056" windowWidth="17280" windowHeight="8880" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1239843B-4C75-4209-B66B-636DD0D50642}"/>
   </bookViews>
   <sheets>
     <sheet name="Famille-Produit" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Famille-Produit'!$A$1:$C$4145</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
   <si>
     <t>Code</t>
   </si>
@@ -58,12 +59,168 @@
   <si>
     <t>Sub Product</t>
   </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Product name</t>
+  </si>
+  <si>
+    <t>FOCUS_DALAA</t>
+  </si>
+  <si>
+    <t>Non Food</t>
+  </si>
+  <si>
+    <t>Dalaa VP / Baqqal / RP</t>
+  </si>
+  <si>
+    <t>FOCUS_CALIN_RP</t>
+  </si>
+  <si>
+    <t>Calin RP</t>
+  </si>
+  <si>
+    <t>FOCUS_MIO_MAIN</t>
+  </si>
+  <si>
+    <t>Mio main (1k+500gr)</t>
+  </si>
+  <si>
+    <t>FOCUS_MIA</t>
+  </si>
+  <si>
+    <t>Mia</t>
+  </si>
+  <si>
+    <t>FOCUS_CALIN_VP</t>
+  </si>
+  <si>
+    <t>Calin VP</t>
+  </si>
+  <si>
+    <t>FOCUS_NOVA</t>
+  </si>
+  <si>
+    <t>Nova</t>
+  </si>
+  <si>
+    <t>FOCUS_PRIMA</t>
+  </si>
+  <si>
+    <t>Prima</t>
+  </si>
+  <si>
+    <t>FOCUS_MIO_LIQ</t>
+  </si>
+  <si>
+    <t>Mio Liquid Vaisselle</t>
+  </si>
+  <si>
+    <t>FOCUS_MIO_JAVEL</t>
+  </si>
+  <si>
+    <t>Mio Javel</t>
+  </si>
+  <si>
+    <t>FOCUS_DOUCEUR</t>
+  </si>
+  <si>
+    <t>Douceur</t>
+  </si>
+  <si>
+    <t>FOCUS_MIO_MATIC</t>
+  </si>
+  <si>
+    <t>Mio Matic</t>
+  </si>
+  <si>
+    <t>FOCUS_PAPILLON</t>
+  </si>
+  <si>
+    <t>Papillon Papier</t>
+  </si>
+  <si>
+    <t>FOCUS_SANGO</t>
+  </si>
+  <si>
+    <t>SANGO</t>
+  </si>
+  <si>
+    <t>FOCUS_BLANDOUX</t>
+  </si>
+  <si>
+    <t>Blandoux</t>
+  </si>
+  <si>
+    <t>FOCUS_SHIWAME</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Shiwame</t>
+  </si>
+  <si>
+    <t>FOCUS_KELLOGGS</t>
+  </si>
+  <si>
+    <t>Kelloggs</t>
+  </si>
+  <si>
+    <t>FOCUS_ITKRANS</t>
+  </si>
+  <si>
+    <t>Al Itkrans + Presto</t>
+  </si>
+  <si>
+    <t>FOCUS_ITKANE</t>
+  </si>
+  <si>
+    <t>FOCUS_TOBIGO</t>
+  </si>
+  <si>
+    <t>Tobigo</t>
+  </si>
+  <si>
+    <t>FOCUS_TAJ</t>
+  </si>
+  <si>
+    <t>TAJ SAHARA</t>
+  </si>
+  <si>
+    <t>FOCUS_MARESOL</t>
+  </si>
+  <si>
+    <t>Maresol</t>
+  </si>
+  <si>
+    <t>FOCUS_TAKYS</t>
+  </si>
+  <si>
+    <t>TAKYS</t>
+  </si>
+  <si>
+    <t>FOCUS_TAWIL</t>
+  </si>
+  <si>
+    <t>Tawil</t>
+  </si>
+  <si>
+    <t>FOCUS_FROMY</t>
+  </si>
+  <si>
+    <t>Fromy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -78,6 +235,21 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
@@ -110,12 +282,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4138,9 +4314,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{04244C09-51F3-4278-BDFC-690C20DEAB9F}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;cac4453d-3c66-4709-bcea-3c2eca781e4c&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0657D201-E0D1-4A21-8365-97823C152015}">
-  <dimension ref="A1:C460"/>
+  <dimension ref="A1:D460"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
@@ -4149,7 +4347,7 @@
     <col min="4" max="4" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4159,8 +4357,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str">
         <f>[1]Products!A930</f>
         <v>CF35250</v>
@@ -4173,8 +4374,11 @@
         <f t="shared" ref="C2:C65" si="0">IF(OR(ISNUMBER(SEARCH("SELHAM",B2)),ISNUMBER(SEARCH("LHAFLA",B2)),ISNUMBER(SEARCH("ZINE",B2)),ISNUMBER(SEARCH("tiyay",B2)),ISNUMBER(SEARCH("alouns",B2)),ISNUMBER(SEARCH("lmhrat",B2))),"The Al Itkane",IF(AND(ISNUMBER(SEARCH("CALIN",B2)),ISNUMBER(SEARCH("RP",B2)),NOT(ISNUMBER(SEARCH("VP",B2)))),"Calin RP",IF(AND(ISNUMBER(SEARCH("CALIN",B2)),ISNUMBER(SEARCH("VP",B2))),"Calin VP",IF(AND(ISNUMBER(SEARCH("MIO",B2)),OR(ISNUMBER(SEARCH("Vaisselle",B2)),ISNUMBER(SEARCH("vaisselle",B2)))),"Mio Liquid Vaisselle",IF(AND(ISNUMBER(SEARCH("MIO",B2)),ISNUMBER(SEARCH("Javel",B2))),"Mio Javel",IF(AND(ISNUMBER(SEARCH("MIO",B2)),ISNUMBER(SEARCH("Matic",B2))),"Mio Matic",IF(AND(ISNUMBER(SEARCH("MIO",B2)),OR(ISNUMBER(SEARCH("Détérgent",B2)),ISNUMBER(SEARCH("Poudre",B2)),ISNUMBER(SEARCH("Semi Auto",B2)),ISNUMBER(SEARCH("1KG",B2)),ISNUMBER(SEARCH("500G",B2)),ISNUMBER(SEARCH("10KG",B2)),ISNUMBER(SEARCH("1.5K",B2)),ISNUMBER(SEARCH("215G",B2)),ISNUMBER(SEARCH("350G",B2)),ISNUMBER(SEARCH("90G",B2)),ISNUMBER(SEARCH("Gold",B2)),ISNUMBER(SEARCH("Citron",B2)),ISNUMBER(SEARCH("Rose",B2)),ISNUMBER(SEARCH("Lessive",B2))),NOT(OR(ISNUMBER(SEARCH("Vaisselle",B2)),ISNUMBER(SEARCH("Javel",B2)),ISNUMBER(SEARCH("Matic",B2)),ISNUMBER(SEARCH("Nettoyant",B2)),ISNUMBER(SEARCH("Pâte",B2)),ISNUMBER(SEARCH("Lave",B2)),ISNUMBER(SEARCH("Détartrant",B2))))),"Mio main (1k+500gr)",IF(AND(ISNUMBER(SEARCH("PAPILLON",B2)),OR(ISNUMBER(SEARCH("Papier",B2)),ISNUMBER(SEARCH("Hygiénique",B2)),ISNUMBER(SEARCH("HYGIÉNIQUE",B2))),NOT(OR(ISNUMBER(SEARCH("Lingette",B2)),ISNUMBER(SEARCH("Mouchoir",B2))))),"Papillon Papier",IF(OR(ISNUMBER(SEARCH("TAJ AL SAHAR",B2)),ISNUMBER(SEARCH("TAJ BLADI",B2)),ISNUMBER(SEARCH("TAJ BELADI",B2)),ISNUMBER(SEARCH("Tilal Assahra",B2)),ISNUMBER(SEARCH("Jawharat Asahra",B2))),"TAJ SAHARA",IF(AND(OR(ISNUMBER(SEARCH("AL ITKANE",B2)),ISNUMBER(SEARCH("ALITKANE",B2)),ISNUMBER(SEARCH("PRESTO",B2))),NOT(OR(ISNUMBER(SEARCH("Thé",B2)),ISNUMBER(SEARCH("THE ",B2)),ISNUMBER(SEARCH("thé",B2)),ISNUMBER(SEARCH("SELHAM",B2)),ISNUMBER(SEARCH("LHAFLA",B2)),ISNUMBER(SEARCH("ZINE",B2)),ISNUMBER(SEARCH("tiyay",B2)),ISNUMBER(SEARCH("alouns",B2)),ISNUMBER(SEARCH("lmhrat",B2))))),"Al Itkrans + Presto",IF(OR(ISNUMBER(SEARCH("DALAA",B2)),ISNUMBER(SEARCH("CS-DALAA",B2)),ISNUMBER(SEARCH("DALINA",B2))),"Dalaa VP / Baqqal / RP",IF(OR(LEFT(UPPER(B2),4)="MIA ",LEFT(UPPER(B2),6)="CS-MIA"),"Mia",IF(OR(LEFT(UPPER(B2),5)="NOVA ",LEFT(UPPER(B2),7)="CS-NOVA"),"Nova",IF(OR(ISNUMBER(SEARCH("PRIMA ",B2)),ISNUMBER(SEARCH("CS-PRIMA",B2))),"Prima",IF(OR(ISNUMBER(SEARCH("Douceur",B2)),ISNUMBER(SEARCH("DOUCEUR",B2))),"Douceur",IF(OR(ISNUMBER(SEARCH("SANGO",B2)),ISNUMBER(SEARCH("CS-SANGO",B2))),"SANGO",IF(ISNUMBER(SEARCH("BLANDOUX",B2)),"Blandoux",IF(ISNUMBER(SEARCH("SHIWAMI",B2)),"Shiwame",IF(ISNUMBER(SEARCH("KELLOGG",B2)),"Kelloggs",IF(OR(ISNUMBER(SEARCH("TOBIGO",B2)),ISNUMBER(SEARCH("DWIST",B2))),"Tobigo",IF(OR(ISNUMBER(SEARCH("MARISOL",B2)),ISNUMBER(SEARCH("MARESOL",B2))),"Maresol",IF(OR(ISNUMBER(SEARCH("TAKIS",B2)),ISNUMBER(SEARCH("TAKYS",B2))),"TAKYS",IF(ISNUMBER(SEARCH("TAWIL",B2)),"Tawil",IF(ISNUMBER(SEARCH("FROMY",B2)),"Fromy",""))))))))))))))))))))))))</f>
         <v>Tobigo</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
         <f>[1]Products!A940</f>
         <v>ART00968</v>
@@ -4187,8 +4391,12 @@
         <f t="shared" si="0"/>
         <v>Tobigo</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="4">
+        <f>IFERROR(VLOOKUP(C3,Feuil1!$C$2:$D$25,2,FALSE),"")</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
         <f>[1]Products!A1125</f>
         <v>CF35266</v>
@@ -4202,7 +4410,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="str">
         <f>[1]Products!A1126</f>
         <v>CF35267</v>
@@ -4216,7 +4424,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="str">
         <f>[1]Products!A1173</f>
         <v>CF35298</v>
@@ -4230,7 +4438,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
         <f>[1]Products!A1229</f>
         <v>CF35516</v>
@@ -4244,7 +4452,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="str">
         <f>[1]Products!A1257</f>
         <v>CF35517</v>
@@ -4258,7 +4466,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="str">
         <f>[1]Products!A1355</f>
         <v>CF35518</v>
@@ -4272,7 +4480,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="str">
         <f>[1]Products!A1422</f>
         <v>ART00221</v>
@@ -4286,7 +4494,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="str">
         <f>[1]Products!A1423</f>
         <v>ART00222</v>
@@ -4300,7 +4508,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="str">
         <f>[1]Products!A1424</f>
         <v>ART00223</v>
@@ -4314,7 +4522,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="str">
         <f>[1]Products!A1425</f>
         <v>ART00224</v>
@@ -4328,7 +4536,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="str">
         <f>[1]Products!A1426</f>
         <v>ART00225</v>
@@ -4342,7 +4550,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="str">
         <f>[1]Products!A1427</f>
         <v>ART00226</v>
@@ -4356,7 +4564,7 @@
         <v>Tobigo</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="str">
         <f>[1]Products!A1428</f>
         <v>ART00227</v>
@@ -10582,4 +10790,370 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCEBC52-2A32-47C0-B2BB-B4F07C47F09D}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>